--- a/data/MI/Penelope/SupplementaryData1_Calculation_Metal_Demand.xlsx
+++ b/data/MI/Penelope/SupplementaryData1_Calculation_Metal_Demand.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/fasc_metal_sustainability/data/MI/Penelope/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{B39B6A3F-D26A-48B9-A17C-949B8561B238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{722CF0D0-0308-41DC-828B-19A244619892}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{B39B6A3F-D26A-48B9-A17C-949B8561B238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43DA72F2-0C90-4D5A-B61A-0121A95940BF}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-705" windowWidth="29040" windowHeight="15720" firstSheet="10" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="-23595" yWindow="4260" windowWidth="14400" windowHeight="7275" firstSheet="10" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table of content" sheetId="26" r:id="rId1"/>
@@ -8665,7 +8665,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B85857DA-147B-4693-A73B-69F8E49F4406}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:G714"/>
@@ -8701,7 +8701,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="84" t="s">
         <v>22</v>
       </c>
@@ -8722,7 +8722,7 @@
       </c>
       <c r="G2" s="84"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="10" t="s">
         <v>22</v>
       </c>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="G3" s="10"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
         <v>22</v>
       </c>
@@ -8765,7 +8765,7 @@
       </c>
       <c r="G4" s="10"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
         <v>22</v>
       </c>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="G5" s="10"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
         <v>22</v>
       </c>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="G6" s="10"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>22</v>
       </c>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="G7" s="10"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
         <v>22</v>
       </c>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="G8" s="10"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10" t="s">
         <v>22</v>
       </c>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="G9" s="10"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="10" t="s">
         <v>22</v>
       </c>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="G10" s="10"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="10" t="s">
         <v>22</v>
       </c>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="G11" s="10"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="10" t="s">
         <v>22</v>
       </c>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="G12" s="10"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="10" t="s">
         <v>22</v>
       </c>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="G13" s="10"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="10" t="s">
         <v>22</v>
       </c>
@@ -8977,7 +8977,7 @@
       </c>
       <c r="G14" s="10"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="10" t="s">
         <v>22</v>
       </c>
@@ -8998,7 +8998,7 @@
       </c>
       <c r="G15" s="10"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="10" t="s">
         <v>22</v>
       </c>
@@ -9020,7 +9020,7 @@
       </c>
       <c r="G16" s="10"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="10" t="s">
         <v>22</v>
       </c>
@@ -9041,7 +9041,7 @@
       </c>
       <c r="G17" s="10"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="10" t="s">
         <v>22</v>
       </c>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="G18" s="10"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -9083,7 +9083,7 @@
       </c>
       <c r="G19" s="10"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="10" t="s">
         <v>22</v>
       </c>
@@ -9104,7 +9104,7 @@
       </c>
       <c r="G20" s="10"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="10" t="s">
         <v>22</v>
       </c>
@@ -9125,7 +9125,7 @@
       </c>
       <c r="G21" s="10"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="10" t="s">
         <v>22</v>
       </c>
@@ -9146,7 +9146,7 @@
       </c>
       <c r="G22" s="10"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="10" t="s">
         <v>22</v>
       </c>
@@ -9167,7 +9167,7 @@
       </c>
       <c r="G23" s="10"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="10" t="s">
         <v>22</v>
       </c>
@@ -9188,7 +9188,7 @@
       </c>
       <c r="G24" s="10"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="10" t="s">
         <v>22</v>
       </c>
@@ -9209,7 +9209,7 @@
       </c>
       <c r="G25" s="10"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="10" t="s">
         <v>495</v>
       </c>
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G26" s="10"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10" t="s">
         <v>495</v>
       </c>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="G27" s="10"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10" t="s">
         <v>495</v>
       </c>
@@ -9272,7 +9272,7 @@
       </c>
       <c r="G28" s="10"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="10" t="s">
         <v>495</v>
       </c>
@@ -9293,7 +9293,7 @@
       </c>
       <c r="G29" s="10"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="10" t="s">
         <v>495</v>
       </c>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="G30" s="10"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="10" t="s">
         <v>495</v>
       </c>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="G31" s="10"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10" t="s">
         <v>495</v>
       </c>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="G32" s="10"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10" t="s">
         <v>495</v>
       </c>
@@ -9377,7 +9377,7 @@
       </c>
       <c r="G33" s="10"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="10" t="s">
         <v>495</v>
       </c>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="G34" s="10"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="10" t="s">
         <v>495</v>
       </c>
@@ -9419,7 +9419,7 @@
       </c>
       <c r="G35" s="10"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="10" t="s">
         <v>495</v>
       </c>
@@ -9440,7 +9440,7 @@
       </c>
       <c r="G36" s="10"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="10" t="s">
         <v>495</v>
       </c>
@@ -9461,7 +9461,7 @@
       </c>
       <c r="G37" s="10"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="10" t="s">
         <v>495</v>
       </c>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="G38" s="10"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="10" t="s">
         <v>495</v>
       </c>
@@ -9503,7 +9503,7 @@
       </c>
       <c r="G39" s="10"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="10" t="s">
         <v>495</v>
       </c>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="G40" s="10"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="10" t="s">
         <v>495</v>
       </c>
@@ -9545,7 +9545,7 @@
       </c>
       <c r="G41" s="10"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="10" t="s">
         <v>495</v>
       </c>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="G42" s="10"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="10" t="s">
         <v>495</v>
       </c>
@@ -9589,7 +9589,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="10" t="s">
         <v>495</v>
       </c>
@@ -9612,7 +9612,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="10" t="s">
         <v>495</v>
       </c>
@@ -9635,7 +9635,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="10" t="s">
         <v>495</v>
       </c>
@@ -9658,7 +9658,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="10" t="s">
         <v>495</v>
       </c>
@@ -9681,7 +9681,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10" t="s">
         <v>495</v>
       </c>
@@ -9702,7 +9702,7 @@
       </c>
       <c r="G48" s="10"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10" t="s">
         <v>495</v>
       </c>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="G49" s="10"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="10" t="s">
         <v>495</v>
       </c>
@@ -9744,7 +9744,7 @@
       </c>
       <c r="G50" s="10"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="10" t="s">
         <v>495</v>
       </c>
@@ -9765,7 +9765,7 @@
       </c>
       <c r="G51" s="10"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="10" t="s">
         <v>495</v>
       </c>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="G52" s="10"/>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="10" t="s">
         <v>495</v>
       </c>
@@ -9807,7 +9807,7 @@
       </c>
       <c r="G53" s="10"/>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="10" t="s">
         <v>495</v>
       </c>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="G54" s="10"/>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="10" t="s">
         <v>495</v>
       </c>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="G55" s="10"/>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="10" t="s">
         <v>495</v>
       </c>
@@ -9870,7 +9870,7 @@
       </c>
       <c r="G56" s="10"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="10" t="s">
         <v>495</v>
       </c>
@@ -9891,7 +9891,7 @@
       </c>
       <c r="G57" s="10"/>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="10" t="s">
         <v>495</v>
       </c>
@@ -9912,7 +9912,7 @@
       </c>
       <c r="G58" s="10"/>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="10" t="s">
         <v>495</v>
       </c>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="G59" s="10"/>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="10" t="s">
         <v>495</v>
       </c>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="G60" s="10"/>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="10" t="s">
         <v>495</v>
       </c>
@@ -9975,7 +9975,7 @@
       </c>
       <c r="G61" s="10"/>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="10" t="s">
         <v>495</v>
       </c>
@@ -9996,7 +9996,7 @@
       </c>
       <c r="G62" s="10"/>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="10" t="s">
         <v>495</v>
       </c>
@@ -10017,7 +10017,7 @@
       </c>
       <c r="G63" s="10"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="10" t="s">
         <v>495</v>
       </c>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="G64" s="10"/>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="10" t="s">
         <v>58</v>
       </c>
@@ -10059,7 +10059,7 @@
       </c>
       <c r="G65" s="10"/>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" s="10" t="s">
         <v>58</v>
       </c>
@@ -10080,7 +10080,7 @@
       </c>
       <c r="G66" s="10"/>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="10" t="s">
         <v>58</v>
       </c>
@@ -10103,7 +10103,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" s="10" t="s">
         <v>58</v>
       </c>
@@ -10124,7 +10124,7 @@
       </c>
       <c r="G68" s="10"/>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" s="10" t="s">
         <v>58</v>
       </c>
@@ -10145,7 +10145,7 @@
       </c>
       <c r="G69" s="10"/>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="10" t="s">
         <v>58</v>
       </c>
@@ -10166,7 +10166,7 @@
       </c>
       <c r="G70" s="10"/>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" s="10" t="s">
         <v>58</v>
       </c>
@@ -10189,7 +10189,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" s="10" t="s">
         <v>58</v>
       </c>
@@ -10210,7 +10210,7 @@
       </c>
       <c r="G72" s="10"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" s="10" t="s">
         <v>58</v>
       </c>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="G73" s="10"/>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" s="10" t="s">
         <v>58</v>
       </c>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="G74" s="10"/>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" s="10" t="s">
         <v>58</v>
       </c>
@@ -10273,7 +10273,7 @@
       </c>
       <c r="G75" s="10"/>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" s="10" t="s">
         <v>58</v>
       </c>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="G76" s="10"/>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" s="10" t="s">
         <v>58</v>
       </c>
@@ -10317,7 +10317,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="10" t="s">
         <v>58</v>
       </c>
@@ -10338,7 +10338,7 @@
       </c>
       <c r="G78" s="10"/>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="10" t="s">
         <v>58</v>
       </c>
@@ -10359,7 +10359,7 @@
       </c>
       <c r="G79" s="10"/>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="10" t="s">
         <v>58</v>
       </c>
@@ -10380,7 +10380,7 @@
       </c>
       <c r="G80" s="10"/>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="10" t="s">
         <v>58</v>
       </c>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="G81" s="10"/>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" s="10" t="s">
         <v>58</v>
       </c>
@@ -10422,7 +10422,7 @@
       </c>
       <c r="G82" s="10"/>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="10" t="s">
         <v>58</v>
       </c>
@@ -10443,7 +10443,7 @@
       </c>
       <c r="G83" s="10"/>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" s="10" t="s">
         <v>58</v>
       </c>
@@ -10464,7 +10464,7 @@
       </c>
       <c r="G84" s="10"/>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="10" t="s">
         <v>58</v>
       </c>
@@ -10485,7 +10485,7 @@
       </c>
       <c r="G85" s="10"/>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" s="10" t="s">
         <v>58</v>
       </c>
@@ -10508,7 +10508,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="10" t="s">
         <v>58</v>
       </c>
@@ -10529,7 +10529,7 @@
       </c>
       <c r="G87" s="10"/>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" s="10" t="s">
         <v>58</v>
       </c>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="G88" s="10"/>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="10" t="s">
         <v>58</v>
       </c>
@@ -10571,7 +10571,7 @@
       </c>
       <c r="G89" s="10"/>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="10" t="s">
         <v>58</v>
       </c>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="G90" s="10"/>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="10" t="s">
         <v>58</v>
       </c>
@@ -10613,7 +10613,7 @@
       </c>
       <c r="G91" s="10"/>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" s="10" t="s">
         <v>58</v>
       </c>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="G92" s="10"/>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10" t="s">
         <v>58</v>
       </c>
@@ -10655,7 +10655,7 @@
       </c>
       <c r="G93" s="10"/>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" s="10" t="s">
         <v>58</v>
       </c>
@@ -10676,7 +10676,7 @@
       </c>
       <c r="G94" s="10"/>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="10" t="s">
         <v>58</v>
       </c>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="G95" s="10"/>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" s="10" t="s">
         <v>58</v>
       </c>
@@ -10718,7 +10718,7 @@
       </c>
       <c r="G96" s="10"/>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" s="10" t="s">
         <v>499</v>
       </c>
@@ -10739,7 +10739,7 @@
       </c>
       <c r="G97" s="10"/>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" s="10" t="s">
         <v>499</v>
       </c>
@@ -10760,7 +10760,7 @@
       </c>
       <c r="G98" s="10"/>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" s="10" t="s">
         <v>499</v>
       </c>
@@ -10781,7 +10781,7 @@
       </c>
       <c r="G99" s="10"/>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" s="10" t="s">
         <v>499</v>
       </c>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="G100" s="10"/>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" s="10" t="s">
         <v>499</v>
       </c>
@@ -10823,7 +10823,7 @@
       </c>
       <c r="G101" s="10"/>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="10" t="s">
         <v>499</v>
       </c>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="G102" s="10"/>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" s="10" t="s">
         <v>499</v>
       </c>
@@ -10865,7 +10865,7 @@
       </c>
       <c r="G103" s="10"/>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" s="10" t="s">
         <v>499</v>
       </c>
@@ -10886,7 +10886,7 @@
       </c>
       <c r="G104" s="10"/>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="10" t="s">
         <v>499</v>
       </c>
@@ -10907,7 +10907,7 @@
       </c>
       <c r="G105" s="10"/>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" s="10" t="s">
         <v>499</v>
       </c>
@@ -10928,7 +10928,7 @@
       </c>
       <c r="G106" s="10"/>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="10" t="s">
         <v>499</v>
       </c>
@@ -10949,7 +10949,7 @@
       </c>
       <c r="G107" s="10"/>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="10" t="s">
         <v>499</v>
       </c>
@@ -10970,7 +10970,7 @@
       </c>
       <c r="G108" s="10"/>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" s="10" t="s">
         <v>499</v>
       </c>
@@ -10991,7 +10991,7 @@
       </c>
       <c r="G109" s="10"/>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" s="10" t="s">
         <v>499</v>
       </c>
@@ -11012,7 +11012,7 @@
       </c>
       <c r="G110" s="10"/>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" s="10" t="s">
         <v>499</v>
       </c>
@@ -11033,7 +11033,7 @@
       </c>
       <c r="G111" s="10"/>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="10" t="s">
         <v>499</v>
       </c>
@@ -11054,7 +11054,7 @@
       </c>
       <c r="G112" s="10"/>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10" t="s">
         <v>499</v>
       </c>
@@ -11075,7 +11075,7 @@
       </c>
       <c r="G113" s="10"/>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" s="10" t="s">
         <v>499</v>
       </c>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="G114" s="10"/>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" s="10" t="s">
         <v>499</v>
       </c>
@@ -11117,7 +11117,7 @@
       </c>
       <c r="G115" s="10"/>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" s="10" t="s">
         <v>499</v>
       </c>
@@ -11138,7 +11138,7 @@
       </c>
       <c r="G116" s="10"/>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" s="10" t="s">
         <v>499</v>
       </c>
@@ -11159,7 +11159,7 @@
       </c>
       <c r="G117" s="10"/>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" s="10" t="s">
         <v>399</v>
       </c>
@@ -11181,7 +11181,7 @@
       </c>
       <c r="G118" s="10"/>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" s="10" t="s">
         <v>399</v>
       </c>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="G119" s="10"/>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" s="10" t="s">
         <v>399</v>
       </c>
@@ -11223,7 +11223,7 @@
       </c>
       <c r="G120" s="10"/>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" s="10" t="s">
         <v>399</v>
       </c>
@@ -11244,7 +11244,7 @@
       </c>
       <c r="G121" s="10"/>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" s="10" t="s">
         <v>399</v>
       </c>
@@ -11265,7 +11265,7 @@
       </c>
       <c r="G122" s="10"/>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" s="10" t="s">
         <v>399</v>
       </c>
@@ -11286,7 +11286,7 @@
       </c>
       <c r="G123" s="10"/>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" s="10" t="s">
         <v>399</v>
       </c>
@@ -11307,7 +11307,7 @@
       </c>
       <c r="G124" s="10"/>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" s="84" t="s">
         <v>399</v>
       </c>
@@ -11328,7 +11328,7 @@
       </c>
       <c r="G125" s="10"/>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" s="10" t="s">
         <v>399</v>
       </c>
@@ -11349,7 +11349,7 @@
       </c>
       <c r="G126" s="10"/>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" s="10" t="s">
         <v>399</v>
       </c>
@@ -11370,7 +11370,7 @@
       </c>
       <c r="G127" s="10"/>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" s="10" t="s">
         <v>399</v>
       </c>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="G128" s="10"/>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" s="10" t="s">
         <v>399</v>
       </c>
@@ -11412,7 +11412,7 @@
       </c>
       <c r="G129" s="10"/>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" s="10" t="s">
         <v>399</v>
       </c>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="G130" s="10"/>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" s="10" t="s">
         <v>399</v>
       </c>
@@ -11454,7 +11454,7 @@
       </c>
       <c r="G131" s="10"/>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" s="10" t="s">
         <v>399</v>
       </c>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="G132" s="10"/>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" s="10" t="s">
         <v>399</v>
       </c>
@@ -11497,7 +11497,7 @@
       </c>
       <c r="G133" s="10"/>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" s="10" t="s">
         <v>399</v>
       </c>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="G134" s="10"/>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" s="10" t="s">
         <v>399</v>
       </c>
@@ -11539,7 +11539,7 @@
       </c>
       <c r="G135" s="10"/>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" s="10" t="s">
         <v>399</v>
       </c>
@@ -11560,7 +11560,7 @@
       </c>
       <c r="G136" s="10"/>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" s="10" t="s">
         <v>399</v>
       </c>
@@ -11581,7 +11581,7 @@
       </c>
       <c r="G137" s="10"/>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" s="10" t="s">
         <v>399</v>
       </c>
@@ -11602,7 +11602,7 @@
       </c>
       <c r="G138" s="10"/>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" s="10" t="s">
         <v>399</v>
       </c>
@@ -11623,7 +11623,7 @@
       </c>
       <c r="G139" s="10"/>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" s="10" t="s">
         <v>399</v>
       </c>
@@ -11644,7 +11644,7 @@
       </c>
       <c r="G140" s="10"/>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" s="10" t="s">
         <v>399</v>
       </c>
@@ -11665,7 +11665,7 @@
       </c>
       <c r="G141" s="10"/>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" s="10" t="s">
         <v>399</v>
       </c>
@@ -11686,7 +11686,7 @@
       </c>
       <c r="G142" s="10"/>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" s="10" t="s">
         <v>399</v>
       </c>
@@ -11707,7 +11707,7 @@
       </c>
       <c r="G143" s="10"/>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" s="10" t="s">
         <v>399</v>
       </c>
@@ -11728,7 +11728,7 @@
       </c>
       <c r="G144" s="10"/>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" s="10" t="s">
         <v>399</v>
       </c>
@@ -11749,7 +11749,7 @@
       </c>
       <c r="G145" s="10"/>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" s="10" t="s">
         <v>399</v>
       </c>
@@ -11770,7 +11770,7 @@
       </c>
       <c r="G146" s="10"/>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" s="10" t="s">
         <v>399</v>
       </c>
@@ -11791,7 +11791,7 @@
       </c>
       <c r="G147" s="10"/>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" s="10" t="s">
         <v>399</v>
       </c>
@@ -11812,7 +11812,7 @@
       </c>
       <c r="G148" s="10"/>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" s="10" t="s">
         <v>399</v>
       </c>
@@ -11833,7 +11833,7 @@
       </c>
       <c r="G149" s="10"/>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" s="10" t="s">
         <v>399</v>
       </c>
@@ -11854,7 +11854,7 @@
       </c>
       <c r="G150" s="10"/>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" s="10" t="s">
         <v>399</v>
       </c>
@@ -11875,7 +11875,7 @@
       </c>
       <c r="G151" s="10"/>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" s="10" t="s">
         <v>399</v>
       </c>
@@ -11896,7 +11896,7 @@
       </c>
       <c r="G152" s="10"/>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" s="10" t="s">
         <v>399</v>
       </c>
@@ -11917,7 +11917,7 @@
       </c>
       <c r="G153" s="10"/>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" s="10" t="s">
         <v>399</v>
       </c>
@@ -11938,7 +11938,7 @@
       </c>
       <c r="G154" s="10"/>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" s="10" t="s">
         <v>399</v>
       </c>
@@ -11959,7 +11959,7 @@
       </c>
       <c r="G155" s="10"/>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" s="10" t="s">
         <v>399</v>
       </c>
@@ -11980,7 +11980,7 @@
       </c>
       <c r="G156" s="10"/>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" s="10" t="s">
         <v>399</v>
       </c>
@@ -12001,7 +12001,7 @@
       </c>
       <c r="G157" s="10"/>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" s="10" t="s">
         <v>399</v>
       </c>
@@ -12022,7 +12022,7 @@
       </c>
       <c r="G158" s="10"/>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" s="10" t="s">
         <v>399</v>
       </c>
@@ -12043,7 +12043,7 @@
       </c>
       <c r="G159" s="10"/>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" s="10" t="s">
         <v>399</v>
       </c>
@@ -12064,7 +12064,7 @@
       </c>
       <c r="G160" s="10"/>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" s="10" t="s">
         <v>399</v>
       </c>
@@ -12085,7 +12085,7 @@
       </c>
       <c r="G161" s="10"/>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" s="10" t="s">
         <v>399</v>
       </c>
@@ -12106,7 +12106,7 @@
       </c>
       <c r="G162" s="10"/>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" s="10" t="s">
         <v>399</v>
       </c>
@@ -12127,7 +12127,7 @@
       </c>
       <c r="G163" s="10"/>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" s="10" t="s">
         <v>399</v>
       </c>
@@ -12148,7 +12148,7 @@
       </c>
       <c r="G164" s="10"/>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" s="10" t="s">
         <v>399</v>
       </c>
@@ -12169,7 +12169,7 @@
       </c>
       <c r="G165" s="10"/>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" s="10" t="s">
         <v>399</v>
       </c>
@@ -12190,7 +12190,7 @@
       </c>
       <c r="G166" s="10"/>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" s="10" t="s">
         <v>399</v>
       </c>
@@ -12211,7 +12211,7 @@
       </c>
       <c r="G167" s="10"/>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" s="10" t="s">
         <v>399</v>
       </c>
@@ -12232,7 +12232,7 @@
       </c>
       <c r="G168" s="10"/>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" s="10" t="s">
         <v>399</v>
       </c>
@@ -12253,7 +12253,7 @@
       </c>
       <c r="G169" s="10"/>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" s="10" t="s">
         <v>399</v>
       </c>
@@ -12274,7 +12274,7 @@
       </c>
       <c r="G170" s="10"/>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" s="10" t="s">
         <v>399</v>
       </c>
@@ -12295,7 +12295,7 @@
       </c>
       <c r="G171" s="10"/>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" s="10" t="s">
         <v>399</v>
       </c>
@@ -12316,7 +12316,7 @@
       </c>
       <c r="G172" s="10"/>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" s="10" t="s">
         <v>399</v>
       </c>
@@ -12337,7 +12337,7 @@
       </c>
       <c r="G173" s="10"/>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" s="10" t="s">
         <v>399</v>
       </c>
@@ -12358,7 +12358,7 @@
       </c>
       <c r="G174" s="10"/>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" s="10" t="s">
         <v>399</v>
       </c>
@@ -12379,7 +12379,7 @@
       </c>
       <c r="G175" s="10"/>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" s="10" t="s">
         <v>399</v>
       </c>
@@ -12400,7 +12400,7 @@
       </c>
       <c r="G176" s="10"/>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" s="10" t="s">
         <v>399</v>
       </c>
@@ -12421,7 +12421,7 @@
       </c>
       <c r="G177" s="10"/>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" s="10" t="s">
         <v>399</v>
       </c>
@@ -12442,7 +12442,7 @@
       </c>
       <c r="G178" s="10"/>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" s="10" t="s">
         <v>399</v>
       </c>
@@ -12463,7 +12463,7 @@
       </c>
       <c r="G179" s="10"/>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" s="10" t="s">
         <v>399</v>
       </c>
@@ -12484,7 +12484,7 @@
       </c>
       <c r="G180" s="10"/>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" s="10" t="s">
         <v>399</v>
       </c>
@@ -12505,7 +12505,7 @@
       </c>
       <c r="G181" s="10"/>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" s="10" t="s">
         <v>399</v>
       </c>
@@ -12526,7 +12526,7 @@
       </c>
       <c r="G182" s="10"/>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" s="10" t="s">
         <v>142</v>
       </c>
@@ -12547,7 +12547,7 @@
       </c>
       <c r="G183" s="10"/>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" s="10" t="s">
         <v>142</v>
       </c>
@@ -12568,7 +12568,7 @@
       </c>
       <c r="G184" s="10"/>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" s="10" t="s">
         <v>142</v>
       </c>
@@ -12589,7 +12589,7 @@
       </c>
       <c r="G185" s="10"/>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" s="10" t="s">
         <v>142</v>
       </c>
@@ -12610,7 +12610,7 @@
       </c>
       <c r="G186" s="10"/>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" s="10" t="s">
         <v>142</v>
       </c>
@@ -12631,7 +12631,7 @@
       </c>
       <c r="G187" s="10"/>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" s="10" t="s">
         <v>142</v>
       </c>
@@ -12652,7 +12652,7 @@
       </c>
       <c r="G188" s="10"/>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" s="10" t="s">
         <v>142</v>
       </c>
@@ -12673,7 +12673,7 @@
       </c>
       <c r="G189" s="10"/>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" s="10" t="s">
         <v>142</v>
       </c>
@@ -12694,7 +12694,7 @@
       </c>
       <c r="G190" s="10"/>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" s="10" t="s">
         <v>142</v>
       </c>
@@ -12715,7 +12715,7 @@
       </c>
       <c r="G191" s="10"/>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" s="10" t="s">
         <v>142</v>
       </c>
@@ -12736,7 +12736,7 @@
       </c>
       <c r="G192" s="10"/>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" s="10" t="s">
         <v>142</v>
       </c>
@@ -12757,7 +12757,7 @@
       </c>
       <c r="G193" s="10"/>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" s="10" t="s">
         <v>142</v>
       </c>
@@ -12778,7 +12778,7 @@
       </c>
       <c r="G194" s="10"/>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" s="10" t="s">
         <v>142</v>
       </c>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="G195" s="10"/>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" s="10" t="s">
         <v>142</v>
       </c>
@@ -12820,7 +12820,7 @@
       </c>
       <c r="G196" s="10"/>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" s="10" t="s">
         <v>142</v>
       </c>
@@ -12841,7 +12841,7 @@
       </c>
       <c r="G197" s="10"/>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" s="10" t="s">
         <v>142</v>
       </c>
@@ -12862,7 +12862,7 @@
       </c>
       <c r="G198" s="10"/>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" s="10" t="s">
         <v>142</v>
       </c>
@@ -12883,7 +12883,7 @@
       </c>
       <c r="G199" s="10"/>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" s="10" t="s">
         <v>142</v>
       </c>
@@ -12904,7 +12904,7 @@
       </c>
       <c r="G200" s="10"/>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" s="10" t="s">
         <v>142</v>
       </c>
@@ -12925,7 +12925,7 @@
       </c>
       <c r="G201" s="10"/>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" s="10" t="s">
         <v>142</v>
       </c>
@@ -12946,7 +12946,7 @@
       </c>
       <c r="G202" s="10"/>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" s="10" t="s">
         <v>142</v>
       </c>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="G203" s="10"/>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" s="10" t="s">
         <v>142</v>
       </c>
@@ -12988,7 +12988,7 @@
       </c>
       <c r="G204" s="10"/>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" s="10" t="s">
         <v>142</v>
       </c>
@@ -13009,7 +13009,7 @@
       </c>
       <c r="G205" s="10"/>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" s="10" t="s">
         <v>142</v>
       </c>
@@ -13030,7 +13030,7 @@
       </c>
       <c r="G206" s="10"/>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" s="10" t="s">
         <v>142</v>
       </c>
@@ -13051,7 +13051,7 @@
       </c>
       <c r="G207" s="10"/>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" s="10" t="s">
         <v>142</v>
       </c>
@@ -13072,7 +13072,7 @@
       </c>
       <c r="G208" s="10"/>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" s="10" t="s">
         <v>142</v>
       </c>
@@ -13093,7 +13093,7 @@
       </c>
       <c r="G209" s="10"/>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" s="10" t="s">
         <v>142</v>
       </c>
@@ -13114,7 +13114,7 @@
       </c>
       <c r="G210" s="10"/>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" s="10" t="s">
         <v>142</v>
       </c>
@@ -13135,7 +13135,7 @@
       </c>
       <c r="G211" s="10"/>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" s="10" t="s">
         <v>142</v>
       </c>
@@ -13156,7 +13156,7 @@
       </c>
       <c r="G212" s="10"/>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" s="10" t="s">
         <v>142</v>
       </c>
@@ -13177,7 +13177,7 @@
       </c>
       <c r="G213" s="10"/>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" s="10" t="s">
         <v>142</v>
       </c>
@@ -13198,7 +13198,7 @@
       </c>
       <c r="G214" s="10"/>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" s="10" t="s">
         <v>142</v>
       </c>
@@ -13219,7 +13219,7 @@
       </c>
       <c r="G215" s="10"/>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" s="10" t="s">
         <v>142</v>
       </c>
@@ -13240,7 +13240,7 @@
       </c>
       <c r="G216" s="10"/>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" s="10" t="s">
         <v>142</v>
       </c>
@@ -13261,7 +13261,7 @@
       </c>
       <c r="G217" s="10"/>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218" s="10" t="s">
         <v>142</v>
       </c>
@@ -13282,7 +13282,7 @@
       </c>
       <c r="G218" s="10"/>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" s="10" t="s">
         <v>142</v>
       </c>
@@ -13303,7 +13303,7 @@
       </c>
       <c r="G219" s="10"/>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" s="10" t="s">
         <v>142</v>
       </c>
@@ -13324,7 +13324,7 @@
       </c>
       <c r="G220" s="10"/>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" s="10" t="s">
         <v>142</v>
       </c>
@@ -13345,7 +13345,7 @@
       </c>
       <c r="G221" s="10"/>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" s="10" t="s">
         <v>142</v>
       </c>
@@ -13366,7 +13366,7 @@
       </c>
       <c r="G222" s="10"/>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" s="10" t="s">
         <v>142</v>
       </c>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="G223" s="10"/>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224" s="10" t="s">
         <v>142</v>
       </c>
@@ -13410,7 +13410,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" s="10" t="s">
         <v>142</v>
       </c>
@@ -13433,7 +13433,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" s="10" t="s">
         <v>142</v>
       </c>
@@ -13454,7 +13454,7 @@
       </c>
       <c r="G226" s="10"/>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" s="10" t="s">
         <v>142</v>
       </c>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="G227" s="10"/>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" s="10" t="s">
         <v>142</v>
       </c>
@@ -13496,7 +13496,7 @@
       </c>
       <c r="G228" s="10"/>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" s="10" t="s">
         <v>142</v>
       </c>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="G229" s="10"/>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" s="10" t="s">
         <v>142</v>
       </c>
@@ -13538,7 +13538,7 @@
       </c>
       <c r="G230" s="10"/>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" s="10" t="s">
         <v>142</v>
       </c>
@@ -13559,7 +13559,7 @@
       </c>
       <c r="G231" s="10"/>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" s="10" t="s">
         <v>142</v>
       </c>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="G232" s="10"/>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" s="10" t="s">
         <v>142</v>
       </c>
@@ -13601,7 +13601,7 @@
       </c>
       <c r="G233" s="10"/>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" s="10" t="s">
         <v>142</v>
       </c>
@@ -13622,7 +13622,7 @@
       </c>
       <c r="G234" s="10"/>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" s="10" t="s">
         <v>142</v>
       </c>
@@ -13643,7 +13643,7 @@
       </c>
       <c r="G235" s="10"/>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" s="10" t="s">
         <v>142</v>
       </c>
@@ -13664,7 +13664,7 @@
       </c>
       <c r="G236" s="10"/>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" s="10" t="s">
         <v>142</v>
       </c>
@@ -13685,7 +13685,7 @@
       </c>
       <c r="G237" s="10"/>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" s="10" t="s">
         <v>142</v>
       </c>
@@ -13706,7 +13706,7 @@
       </c>
       <c r="G238" s="10"/>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" s="10" t="s">
         <v>142</v>
       </c>
@@ -13727,7 +13727,7 @@
       </c>
       <c r="G239" s="10"/>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" s="10" t="s">
         <v>142</v>
       </c>
@@ -13748,7 +13748,7 @@
       </c>
       <c r="G240" s="10"/>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" s="10" t="s">
         <v>142</v>
       </c>
@@ -13769,7 +13769,7 @@
       </c>
       <c r="G241" s="10"/>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" s="10" t="s">
         <v>142</v>
       </c>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="G242" s="10"/>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" s="10" t="s">
         <v>142</v>
       </c>
@@ -13811,7 +13811,7 @@
       </c>
       <c r="G243" s="10"/>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" s="10" t="s">
         <v>142</v>
       </c>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="G244" s="10"/>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" s="10" t="s">
         <v>141</v>
       </c>
@@ -13853,7 +13853,7 @@
       </c>
       <c r="G245" s="10"/>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" s="10" t="s">
         <v>141</v>
       </c>
@@ -13875,7 +13875,7 @@
       </c>
       <c r="G246" s="10"/>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" s="10" t="s">
         <v>141</v>
       </c>
@@ -13896,7 +13896,7 @@
       </c>
       <c r="G247" s="10"/>
     </row>
-    <row r="248" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:7" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="10" t="s">
         <v>141</v>
       </c>
@@ -13917,7 +13917,7 @@
       </c>
       <c r="G248" s="10"/>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" s="10" t="s">
         <v>141</v>
       </c>
@@ -13938,7 +13938,7 @@
       </c>
       <c r="G249" s="10"/>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" s="10" t="s">
         <v>141</v>
       </c>
@@ -13959,7 +13959,7 @@
       </c>
       <c r="G250" s="10"/>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" s="10" t="s">
         <v>141</v>
       </c>
@@ -13982,7 +13982,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" s="10" t="s">
         <v>141</v>
       </c>
@@ -14005,7 +14005,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" s="10" t="s">
         <v>141</v>
       </c>
@@ -14028,7 +14028,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" s="10" t="s">
         <v>141</v>
       </c>
@@ -14051,7 +14051,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" s="10" t="s">
         <v>141</v>
       </c>
@@ -14074,7 +14074,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" s="10" t="s">
         <v>141</v>
       </c>
@@ -14097,7 +14097,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" s="10" t="s">
         <v>141</v>
       </c>
@@ -14118,7 +14118,7 @@
       </c>
       <c r="G257" s="10"/>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" s="10" t="s">
         <v>141</v>
       </c>
@@ -14141,7 +14141,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" s="10" t="s">
         <v>141</v>
       </c>
@@ -14162,7 +14162,7 @@
       </c>
       <c r="G259" s="10"/>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" s="10" t="s">
         <v>141</v>
       </c>
@@ -14185,7 +14185,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="261" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:7" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261" s="10" t="s">
         <v>141</v>
       </c>
@@ -14206,7 +14206,7 @@
       </c>
       <c r="G261" s="10"/>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" s="10" t="s">
         <v>141</v>
       </c>
@@ -14229,7 +14229,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" s="10" t="s">
         <v>141</v>
       </c>
@@ -14252,7 +14252,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" s="10" t="s">
         <v>141</v>
       </c>
@@ -14273,7 +14273,7 @@
       </c>
       <c r="G264" s="10"/>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" s="10" t="s">
         <v>141</v>
       </c>
@@ -14294,7 +14294,7 @@
       </c>
       <c r="G265" s="10"/>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" s="10" t="s">
         <v>141</v>
       </c>
@@ -14315,7 +14315,7 @@
       </c>
       <c r="G266" s="10"/>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" s="10" t="s">
         <v>141</v>
       </c>
@@ -14336,7 +14336,7 @@
       </c>
       <c r="G267" s="10"/>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" s="10" t="s">
         <v>141</v>
       </c>
@@ -14357,7 +14357,7 @@
       </c>
       <c r="G268" s="10"/>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269" s="10" t="s">
         <v>141</v>
       </c>
@@ -14378,7 +14378,7 @@
       </c>
       <c r="G269" s="10"/>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" s="10" t="s">
         <v>141</v>
       </c>
@@ -14399,7 +14399,7 @@
       </c>
       <c r="G270" s="10"/>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" s="10" t="s">
         <v>141</v>
       </c>
@@ -14421,7 +14421,7 @@
       </c>
       <c r="G271" s="10"/>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" s="10" t="s">
         <v>141</v>
       </c>
@@ -14442,7 +14442,7 @@
       </c>
       <c r="G272" s="10"/>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273" s="10" t="s">
         <v>141</v>
       </c>
@@ -14463,7 +14463,7 @@
       </c>
       <c r="G273" s="10"/>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274" s="10" t="s">
         <v>141</v>
       </c>
@@ -14486,7 +14486,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275" s="10" t="s">
         <v>141</v>
       </c>
@@ -14507,7 +14507,7 @@
       </c>
       <c r="G275" s="10"/>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" s="10" t="s">
         <v>141</v>
       </c>
@@ -14528,7 +14528,7 @@
       </c>
       <c r="G276" s="10"/>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" s="10" t="s">
         <v>141</v>
       </c>
@@ -14551,7 +14551,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" s="10" t="s">
         <v>141</v>
       </c>
@@ -14572,7 +14572,7 @@
       </c>
       <c r="G278" s="10"/>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" s="10" t="s">
         <v>141</v>
       </c>
@@ -14593,7 +14593,7 @@
       </c>
       <c r="G279" s="10"/>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" s="10" t="s">
         <v>141</v>
       </c>
@@ -14616,7 +14616,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="281" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:7" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" s="10" t="s">
         <v>141</v>
       </c>
@@ -14637,7 +14637,7 @@
       </c>
       <c r="G281" s="10"/>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" s="10" t="s">
         <v>141</v>
       </c>
@@ -14660,7 +14660,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" s="10" t="s">
         <v>141</v>
       </c>
@@ -14681,7 +14681,7 @@
       </c>
       <c r="G283" s="10"/>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284" s="10" t="s">
         <v>141</v>
       </c>
@@ -14704,7 +14704,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" s="10" t="s">
         <v>141</v>
       </c>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="G285" s="10"/>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" s="10" t="s">
         <v>141</v>
       </c>
@@ -14746,7 +14746,7 @@
       </c>
       <c r="G286" s="10"/>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287" s="10" t="s">
         <v>141</v>
       </c>
@@ -14769,7 +14769,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="288" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:7" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" s="10" t="s">
         <v>141</v>
       </c>
@@ -14790,7 +14790,7 @@
       </c>
       <c r="G288" s="10"/>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" s="10" t="s">
         <v>141</v>
       </c>
@@ -14811,7 +14811,7 @@
       </c>
       <c r="G289" s="10"/>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290" s="10" t="s">
         <v>141</v>
       </c>
@@ -14832,7 +14832,7 @@
       </c>
       <c r="G290" s="10"/>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291" s="10" t="s">
         <v>141</v>
       </c>
@@ -14853,7 +14853,7 @@
       </c>
       <c r="G291" s="10"/>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292" s="10" t="s">
         <v>141</v>
       </c>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="G292" s="10"/>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" s="10" t="s">
         <v>141</v>
       </c>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="G293" s="10"/>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294" s="10" t="s">
         <v>141</v>
       </c>
@@ -14916,7 +14916,7 @@
       </c>
       <c r="G294" s="10"/>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A295" s="10" t="s">
         <v>141</v>
       </c>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="G295" s="10"/>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A296" s="10" t="s">
         <v>141</v>
       </c>
@@ -14958,7 +14958,7 @@
       </c>
       <c r="G296" s="10"/>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297" s="10" t="s">
         <v>141</v>
       </c>
@@ -14979,7 +14979,7 @@
       </c>
       <c r="G297" s="10"/>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" s="10" t="s">
         <v>141</v>
       </c>
@@ -15000,7 +15000,7 @@
       </c>
       <c r="G298" s="10"/>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299" s="10" t="s">
         <v>141</v>
       </c>
@@ -15023,7 +15023,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A300" s="10" t="s">
         <v>141</v>
       </c>
@@ -15044,7 +15044,7 @@
       </c>
       <c r="G300" s="10"/>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301" s="10" t="s">
         <v>141</v>
       </c>
@@ -15065,7 +15065,7 @@
       </c>
       <c r="G301" s="10"/>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302" s="10" t="s">
         <v>141</v>
       </c>
@@ -15088,7 +15088,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A303" s="10" t="s">
         <v>141</v>
       </c>
@@ -15111,7 +15111,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304" s="10" t="s">
         <v>141</v>
       </c>
@@ -15134,7 +15134,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305" s="10" t="s">
         <v>141</v>
       </c>
@@ -15157,7 +15157,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A306" s="10" t="s">
         <v>141</v>
       </c>
@@ -15180,7 +15180,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A307" s="10" t="s">
         <v>141</v>
       </c>
@@ -15203,7 +15203,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A308" s="10" t="s">
         <v>141</v>
       </c>
@@ -15226,7 +15226,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="309" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:7" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A309" s="10" t="s">
         <v>141</v>
       </c>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="G309" s="10"/>
     </row>
-    <row r="310" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:7" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A310" s="10" t="s">
         <v>141</v>
       </c>
@@ -15270,7 +15270,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A311" s="10" t="s">
         <v>141</v>
       </c>
@@ -15293,7 +15293,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A312" s="10" t="s">
         <v>141</v>
       </c>
@@ -15314,7 +15314,7 @@
       </c>
       <c r="G312" s="10"/>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A313" s="84" t="s">
         <v>141</v>
       </c>
@@ -15337,7 +15337,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A314" s="10" t="s">
         <v>141</v>
       </c>
@@ -15358,7 +15358,7 @@
       </c>
       <c r="G314" s="10"/>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A315" s="10" t="s">
         <v>141</v>
       </c>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="G315" s="10"/>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A316" s="10" t="s">
         <v>141</v>
       </c>
@@ -15402,7 +15402,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A317" s="10" t="s">
         <v>141</v>
       </c>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="G317" s="10"/>
     </row>
-    <row r="318" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:7" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A318" s="10" t="s">
         <v>141</v>
       </c>
@@ -15444,7 +15444,7 @@
       </c>
       <c r="G318" s="10"/>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A319" s="10" t="s">
         <v>141</v>
       </c>
@@ -15467,7 +15467,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A320" s="10" t="s">
         <v>141</v>
       </c>
@@ -15490,7 +15490,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A321" s="10" t="s">
         <v>141</v>
       </c>
@@ -15513,7 +15513,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A322" s="84" t="s">
         <v>141</v>
       </c>
@@ -15534,7 +15534,7 @@
       </c>
       <c r="G322" s="84"/>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A323" s="10" t="s">
         <v>141</v>
       </c>
@@ -15557,7 +15557,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A324" s="10" t="s">
         <v>141</v>
       </c>
@@ -15578,7 +15578,7 @@
       </c>
       <c r="G324" s="10"/>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A325" s="10" t="s">
         <v>141</v>
       </c>
@@ -15601,7 +15601,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="326" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:7" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A326" s="10" t="s">
         <v>141</v>
       </c>
@@ -15622,7 +15622,7 @@
       </c>
       <c r="G326" s="10"/>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A327" s="10" t="s">
         <v>141</v>
       </c>
@@ -15645,7 +15645,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A328" s="10" t="s">
         <v>141</v>
       </c>
@@ -15666,7 +15666,7 @@
       </c>
       <c r="G328" s="10"/>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A329" s="10" t="s">
         <v>141</v>
       </c>
@@ -15687,7 +15687,7 @@
       </c>
       <c r="G329" s="10"/>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A330" s="10" t="s">
         <v>141</v>
       </c>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="G330" s="10"/>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A331" s="10" t="s">
         <v>141</v>
       </c>
@@ -15729,7 +15729,7 @@
       </c>
       <c r="G331" s="10"/>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A332" s="10" t="s">
         <v>141</v>
       </c>
@@ -15750,7 +15750,7 @@
       </c>
       <c r="G332" s="10"/>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A333" s="10" t="s">
         <v>141</v>
       </c>
@@ -15771,7 +15771,7 @@
       </c>
       <c r="G333" s="10"/>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A334" s="10" t="s">
         <v>141</v>
       </c>
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G334" s="10"/>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A335" s="10" t="s">
         <v>141</v>
       </c>
@@ -15815,7 +15815,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A336" s="10" t="s">
         <v>141</v>
       </c>
@@ -15836,7 +15836,7 @@
       </c>
       <c r="G336" s="10"/>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A337" s="10" t="s">
         <v>141</v>
       </c>
@@ -15857,7 +15857,7 @@
       </c>
       <c r="G337" s="10"/>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A338" s="10" t="s">
         <v>141</v>
       </c>
@@ -15880,7 +15880,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A339" s="10" t="s">
         <v>141</v>
       </c>
@@ -15901,7 +15901,7 @@
       </c>
       <c r="G339" s="10"/>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A340" s="10" t="s">
         <v>141</v>
       </c>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="G340" s="10"/>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A341" s="10" t="s">
         <v>141</v>
       </c>
@@ -15943,7 +15943,7 @@
       </c>
       <c r="G341" s="10"/>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A342" s="10" t="s">
         <v>141</v>
       </c>
@@ -15966,7 +15966,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A343" s="10" t="s">
         <v>141</v>
       </c>
@@ -15987,7 +15987,7 @@
       </c>
       <c r="G343" s="10"/>
     </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A344" s="10" t="s">
         <v>141</v>
       </c>
@@ -16010,7 +16010,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A345" s="10" t="s">
         <v>141</v>
       </c>
@@ -16031,7 +16031,7 @@
       </c>
       <c r="G345" s="10"/>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A346" s="10" t="s">
         <v>141</v>
       </c>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="G346" s="10"/>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A347" s="10" t="s">
         <v>141</v>
       </c>
@@ -16073,7 +16073,7 @@
       </c>
       <c r="G347" s="10"/>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A348" s="10" t="s">
         <v>141</v>
       </c>
@@ -16096,7 +16096,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A349" s="10" t="s">
         <v>141</v>
       </c>
@@ -16117,7 +16117,7 @@
       </c>
       <c r="G349" s="10"/>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A350" s="10" t="s">
         <v>141</v>
       </c>
@@ -16138,7 +16138,7 @@
       </c>
       <c r="G350" s="10"/>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A351" s="10" t="s">
         <v>141</v>
       </c>
@@ -16159,7 +16159,7 @@
       </c>
       <c r="G351" s="10"/>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A352" s="10" t="s">
         <v>141</v>
       </c>
@@ -16182,7 +16182,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="353" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:7" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A353" s="10" t="s">
         <v>141</v>
       </c>
@@ -16203,7 +16203,7 @@
       </c>
       <c r="G353" s="10"/>
     </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A354" s="10" t="s">
         <v>141</v>
       </c>
@@ -16224,7 +16224,7 @@
       </c>
       <c r="G354" s="10"/>
     </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A355" s="10" t="s">
         <v>141</v>
       </c>
@@ -16247,7 +16247,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A356" s="10" t="s">
         <v>141</v>
       </c>
@@ -16268,7 +16268,7 @@
       </c>
       <c r="G356" s="10"/>
     </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A357" s="10" t="s">
         <v>141</v>
       </c>
@@ -16289,7 +16289,7 @@
       </c>
       <c r="G357" s="10"/>
     </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A358" s="10" t="s">
         <v>141</v>
       </c>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="G358" s="10"/>
     </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A359" s="10" t="s">
         <v>141</v>
       </c>
@@ -16333,7 +16333,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A360" s="10" t="s">
         <v>141</v>
       </c>
@@ -16354,7 +16354,7 @@
       </c>
       <c r="G360" s="10"/>
     </row>
-    <row r="361" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:7" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A361" s="10" t="s">
         <v>141</v>
       </c>
@@ -16375,7 +16375,7 @@
       </c>
       <c r="G361" s="10"/>
     </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A362" s="10" t="s">
         <v>141</v>
       </c>
@@ -16398,7 +16398,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="363" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:7" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A363" s="10" t="s">
         <v>141</v>
       </c>
@@ -16419,7 +16419,7 @@
       </c>
       <c r="G363" s="10"/>
     </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A364" s="10" t="s">
         <v>141</v>
       </c>
@@ -16442,7 +16442,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A365" s="10" t="s">
         <v>141</v>
       </c>
@@ -16463,7 +16463,7 @@
       </c>
       <c r="G365" s="10"/>
     </row>
-    <row r="366" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:7" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A366" s="10" t="s">
         <v>141</v>
       </c>
@@ -16484,7 +16484,7 @@
       </c>
       <c r="G366" s="10"/>
     </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A367" s="10" t="s">
         <v>141</v>
       </c>
@@ -16507,7 +16507,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A368" s="10" t="s">
         <v>141</v>
       </c>
@@ -16530,7 +16530,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A369" s="10" t="s">
         <v>516</v>
       </c>
@@ -16553,7 +16553,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A370" s="10" t="s">
         <v>516</v>
       </c>
@@ -16643,7 +16643,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A374" s="10" t="s">
         <v>516</v>
       </c>
@@ -16689,7 +16689,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A376" s="10" t="s">
         <v>516</v>
       </c>
@@ -16712,7 +16712,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A377" s="10" t="s">
         <v>516</v>
       </c>
@@ -16735,7 +16735,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A378" s="10" t="s">
         <v>516</v>
       </c>
@@ -16756,7 +16756,7 @@
       </c>
       <c r="G378" s="10"/>
     </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A379" s="10" t="s">
         <v>516</v>
       </c>
@@ -16777,7 +16777,7 @@
       </c>
       <c r="G379" s="10"/>
     </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A380" s="10" t="s">
         <v>516</v>
       </c>
@@ -16823,7 +16823,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A382" s="10" t="s">
         <v>516</v>
       </c>
@@ -16892,7 +16892,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A385" s="10" t="s">
         <v>516</v>
       </c>
@@ -16915,7 +16915,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A386" s="10" t="s">
         <v>516</v>
       </c>
@@ -16938,7 +16938,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A387" s="10" t="s">
         <v>516</v>
       </c>
@@ -16984,7 +16984,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A389" s="10" t="s">
         <v>516</v>
       </c>
@@ -17028,7 +17028,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A391" s="10" t="s">
         <v>516</v>
       </c>
@@ -17051,7 +17051,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A392" s="10" t="s">
         <v>516</v>
       </c>
@@ -17072,7 +17072,7 @@
       </c>
       <c r="G392" s="10"/>
     </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A393" s="10" t="s">
         <v>516</v>
       </c>
@@ -17095,7 +17095,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A394" s="10" t="s">
         <v>516</v>
       </c>
@@ -17204,7 +17204,7 @@
       </c>
       <c r="G398" s="10"/>
     </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A399" s="10" t="s">
         <v>516</v>
       </c>
@@ -17225,7 +17225,7 @@
       </c>
       <c r="G399" s="10"/>
     </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A400" s="10" t="s">
         <v>516</v>
       </c>
@@ -17246,7 +17246,7 @@
       </c>
       <c r="G400" s="10"/>
     </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A401" s="10" t="s">
         <v>516</v>
       </c>
@@ -17269,7 +17269,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A402" s="10" t="s">
         <v>516</v>
       </c>
@@ -17292,7 +17292,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A403" s="10" t="s">
         <v>516</v>
       </c>
@@ -17315,7 +17315,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A404" s="10" t="s">
         <v>516</v>
       </c>
@@ -17361,7 +17361,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A406" s="10" t="s">
         <v>516</v>
       </c>
@@ -17384,7 +17384,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A407" s="10" t="s">
         <v>516</v>
       </c>
@@ -17430,7 +17430,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A409" s="10" t="s">
         <v>516</v>
       </c>
@@ -17453,7 +17453,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A410" s="10" t="s">
         <v>516</v>
       </c>
@@ -17476,7 +17476,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A411" s="10" t="s">
         <v>516</v>
       </c>
@@ -17497,7 +17497,7 @@
       </c>
       <c r="G411" s="10"/>
     </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A412" s="10" t="s">
         <v>516</v>
       </c>
@@ -17518,7 +17518,7 @@
       </c>
       <c r="G412" s="10"/>
     </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A413" s="10" t="s">
         <v>516</v>
       </c>
@@ -17541,7 +17541,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A414" s="10" t="s">
         <v>516</v>
       </c>
@@ -17564,7 +17564,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A415" s="10" t="s">
         <v>516</v>
       </c>
@@ -17587,7 +17587,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A416" s="10" t="s">
         <v>516</v>
       </c>
@@ -17610,7 +17610,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A417" s="10" t="s">
         <v>516</v>
       </c>
@@ -17633,7 +17633,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A418" s="10" t="s">
         <v>516</v>
       </c>
@@ -17654,7 +17654,7 @@
       </c>
       <c r="G418" s="10"/>
     </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A419" s="10" t="s">
         <v>516</v>
       </c>
@@ -17675,7 +17675,7 @@
       </c>
       <c r="G419" s="10"/>
     </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A420" s="10" t="s">
         <v>516</v>
       </c>
@@ -17742,7 +17742,7 @@
       </c>
       <c r="G422" s="10"/>
     </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A423" s="10" t="s">
         <v>516</v>
       </c>
@@ -17765,7 +17765,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A424" s="10" t="s">
         <v>516</v>
       </c>
@@ -17788,7 +17788,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A425" s="10" t="s">
         <v>516</v>
       </c>
@@ -17809,7 +17809,7 @@
       </c>
       <c r="G425" s="10"/>
     </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A426" s="10" t="s">
         <v>516</v>
       </c>
@@ -17833,7 +17833,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A427" s="10" t="s">
         <v>516</v>
       </c>
@@ -17856,7 +17856,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A428" s="10" t="s">
         <v>516</v>
       </c>
@@ -17902,7 +17902,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A430" s="10" t="s">
         <v>516</v>
       </c>
@@ -17925,7 +17925,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A431" s="10" t="s">
         <v>516</v>
       </c>
@@ -17948,7 +17948,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A432" s="10" t="s">
         <v>516</v>
       </c>
@@ -17971,7 +17971,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A433" s="10" t="s">
         <v>516</v>
       </c>
@@ -18017,7 +18017,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A435" s="10" t="s">
         <v>516</v>
       </c>
@@ -18040,7 +18040,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A436" s="10" t="s">
         <v>516</v>
       </c>
@@ -18061,7 +18061,7 @@
       </c>
       <c r="G436" s="10"/>
     </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A437" s="10" t="s">
         <v>516</v>
       </c>
@@ -18084,7 +18084,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A438" s="10" t="s">
         <v>516</v>
       </c>
@@ -18107,7 +18107,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A439" s="10" t="s">
         <v>516</v>
       </c>
@@ -18128,7 +18128,7 @@
       </c>
       <c r="G439" s="10"/>
     </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A440" s="10" t="s">
         <v>516</v>
       </c>
@@ -18151,7 +18151,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A441" s="10" t="s">
         <v>516</v>
       </c>
@@ -18174,7 +18174,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A442" s="10" t="s">
         <v>516</v>
       </c>
@@ -18197,7 +18197,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A443" s="10" t="s">
         <v>516</v>
       </c>
@@ -18220,7 +18220,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A444" s="10" t="s">
         <v>516</v>
       </c>
@@ -18243,7 +18243,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A445" s="10" t="s">
         <v>516</v>
       </c>
@@ -18266,7 +18266,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A446" s="10" t="s">
         <v>516</v>
       </c>
@@ -18289,7 +18289,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A447" s="10" t="s">
         <v>516</v>
       </c>
@@ -18312,7 +18312,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A448" s="10" t="s">
         <v>516</v>
       </c>
@@ -18335,7 +18335,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A449" s="10" t="s">
         <v>516</v>
       </c>
@@ -18358,7 +18358,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A450" s="10" t="s">
         <v>516</v>
       </c>
@@ -18381,7 +18381,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A451" s="10" t="s">
         <v>516</v>
       </c>
@@ -18404,7 +18404,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A452" s="10" t="s">
         <v>516</v>
       </c>
@@ -18427,7 +18427,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A453" s="10" t="s">
         <v>516</v>
       </c>
@@ -18450,7 +18450,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A454" s="10" t="s">
         <v>516</v>
       </c>
@@ -18473,7 +18473,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A455" s="10" t="s">
         <v>516</v>
       </c>
@@ -18494,7 +18494,7 @@
       </c>
       <c r="G455" s="10"/>
     </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A456" s="10" t="s">
         <v>516</v>
       </c>
@@ -18515,7 +18515,7 @@
       </c>
       <c r="G456" s="10"/>
     </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A457" s="10" t="s">
         <v>516</v>
       </c>
@@ -18536,7 +18536,7 @@
       </c>
       <c r="G457" s="10"/>
     </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A458" s="10" t="s">
         <v>516</v>
       </c>
@@ -18557,7 +18557,7 @@
       </c>
       <c r="G458" s="10"/>
     </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A459" s="10" t="s">
         <v>516</v>
       </c>
@@ -18580,7 +18580,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A460" s="10" t="s">
         <v>516</v>
       </c>
@@ -18603,7 +18603,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A461" s="10" t="s">
         <v>516</v>
       </c>
@@ -18626,7 +18626,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A462" s="10" t="s">
         <v>516</v>
       </c>
@@ -18649,7 +18649,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A463" s="10" t="s">
         <v>516</v>
       </c>
@@ -18672,7 +18672,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="464" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A464" s="10" t="s">
         <v>516</v>
       </c>
@@ -18695,7 +18695,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A465" s="10" t="s">
         <v>516</v>
       </c>
@@ -18718,7 +18718,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A466" s="10" t="s">
         <v>516</v>
       </c>
@@ -18739,7 +18739,7 @@
       </c>
       <c r="G466" s="10"/>
     </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A467" s="10" t="s">
         <v>516</v>
       </c>
@@ -18762,7 +18762,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A468" s="10" t="s">
         <v>516</v>
       </c>
@@ -18785,7 +18785,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A469" s="10" t="s">
         <v>516</v>
       </c>
@@ -18808,7 +18808,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A470" s="10" t="s">
         <v>516</v>
       </c>
@@ -18831,7 +18831,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A471" s="10" t="s">
         <v>516</v>
       </c>
@@ -18854,7 +18854,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A472" s="10" t="s">
         <v>516</v>
       </c>
@@ -18875,7 +18875,7 @@
       </c>
       <c r="G472" s="10"/>
     </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A473" s="10" t="s">
         <v>516</v>
       </c>
@@ -18898,7 +18898,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A474" s="10" t="s">
         <v>516</v>
       </c>
@@ -18921,7 +18921,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A475" s="10" t="s">
         <v>516</v>
       </c>
@@ -18942,7 +18942,7 @@
       </c>
       <c r="G475" s="10"/>
     </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A476" s="10" t="s">
         <v>516</v>
       </c>
@@ -18965,7 +18965,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A477" s="10" t="s">
         <v>516</v>
       </c>
@@ -18988,7 +18988,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A478" s="10" t="s">
         <v>516</v>
       </c>
@@ -19009,7 +19009,7 @@
       </c>
       <c r="G478" s="10"/>
     </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A479" s="10" t="s">
         <v>516</v>
       </c>
@@ -19032,7 +19032,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A480" s="10" t="s">
         <v>516</v>
       </c>
@@ -19053,7 +19053,7 @@
       </c>
       <c r="G480" s="10"/>
     </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A481" s="10" t="s">
         <v>516</v>
       </c>
@@ -19076,7 +19076,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A482" s="10" t="s">
         <v>516</v>
       </c>
@@ -19099,7 +19099,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A483" s="10" t="s">
         <v>516</v>
       </c>
@@ -19120,7 +19120,7 @@
       </c>
       <c r="G483" s="10"/>
     </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A484" s="10" t="s">
         <v>516</v>
       </c>
@@ -19143,7 +19143,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A485" s="10" t="s">
         <v>516</v>
       </c>
@@ -19164,7 +19164,7 @@
       </c>
       <c r="G485" s="10"/>
     </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A486" s="10" t="s">
         <v>516</v>
       </c>
@@ -19187,7 +19187,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A487" s="10" t="s">
         <v>516</v>
       </c>
@@ -19208,7 +19208,7 @@
       </c>
       <c r="G487" s="10"/>
     </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A488" s="10" t="s">
         <v>516</v>
       </c>
@@ -19231,7 +19231,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A489" s="10" t="s">
         <v>516</v>
       </c>
@@ -19254,7 +19254,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A490" s="10" t="s">
         <v>516</v>
       </c>
@@ -19277,7 +19277,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A491" s="10" t="s">
         <v>516</v>
       </c>
@@ -19300,7 +19300,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A492" s="10" t="s">
         <v>516</v>
       </c>
@@ -19323,7 +19323,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A493" s="10" t="s">
         <v>516</v>
       </c>
@@ -19346,7 +19346,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A494" s="10" t="s">
         <v>516</v>
       </c>
@@ -19369,7 +19369,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="495" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A495" s="10" t="s">
         <v>516</v>
       </c>
@@ -19392,7 +19392,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A496" s="10" t="s">
         <v>516</v>
       </c>
@@ -19415,7 +19415,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="497" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A497" s="10" t="s">
         <v>516</v>
       </c>
@@ -19438,7 +19438,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="498" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A498" s="10" t="s">
         <v>516</v>
       </c>
@@ -19461,7 +19461,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="499" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A499" s="10" t="s">
         <v>516</v>
       </c>
@@ -19484,7 +19484,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="500" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A500" s="10" t="s">
         <v>516</v>
       </c>
@@ -19507,7 +19507,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="501" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A501" s="10" t="s">
         <v>516</v>
       </c>
@@ -19530,7 +19530,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="502" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A502" s="10" t="s">
         <v>516</v>
       </c>
@@ -19553,7 +19553,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="503" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A503" s="10" t="s">
         <v>516</v>
       </c>
@@ -19576,7 +19576,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="504" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A504" s="10" t="s">
         <v>516</v>
       </c>
@@ -19599,7 +19599,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="505" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A505" s="10" t="s">
         <v>516</v>
       </c>
@@ -19622,7 +19622,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="506" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A506" s="10" t="s">
         <v>516</v>
       </c>
@@ -19645,7 +19645,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="507" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A507" s="10" t="s">
         <v>516</v>
       </c>
@@ -19668,7 +19668,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="508" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A508" s="10" t="s">
         <v>516</v>
       </c>
@@ -19689,7 +19689,7 @@
       </c>
       <c r="G508" s="10"/>
     </row>
-    <row r="509" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A509" s="10" t="s">
         <v>516</v>
       </c>
@@ -19710,7 +19710,7 @@
       </c>
       <c r="G509" s="10"/>
     </row>
-    <row r="510" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A510" s="10" t="s">
         <v>516</v>
       </c>
@@ -19731,7 +19731,7 @@
       </c>
       <c r="G510" s="10"/>
     </row>
-    <row r="511" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A511" s="10" t="s">
         <v>516</v>
       </c>
@@ -19752,7 +19752,7 @@
       </c>
       <c r="G511" s="10"/>
     </row>
-    <row r="512" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A512" s="10" t="s">
         <v>555</v>
       </c>
@@ -19773,7 +19773,7 @@
       </c>
       <c r="G512" s="10"/>
     </row>
-    <row r="513" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A513" s="10" t="s">
         <v>555</v>
       </c>
@@ -19794,7 +19794,7 @@
       </c>
       <c r="G513" s="10"/>
     </row>
-    <row r="514" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A514" s="10" t="s">
         <v>555</v>
       </c>
@@ -19815,7 +19815,7 @@
       </c>
       <c r="G514" s="10"/>
     </row>
-    <row r="515" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A515" s="10" t="s">
         <v>555</v>
       </c>
@@ -19836,7 +19836,7 @@
       </c>
       <c r="G515" s="10"/>
     </row>
-    <row r="516" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A516" s="10" t="s">
         <v>555</v>
       </c>
@@ -19857,7 +19857,7 @@
       </c>
       <c r="G516" s="10"/>
     </row>
-    <row r="517" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A517" s="10" t="s">
         <v>555</v>
       </c>
@@ -19899,7 +19899,7 @@
       </c>
       <c r="G518" s="10"/>
     </row>
-    <row r="519" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A519" s="10" t="s">
         <v>555</v>
       </c>
@@ -19920,7 +19920,7 @@
       </c>
       <c r="G519" s="10"/>
     </row>
-    <row r="520" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A520" s="10" t="s">
         <v>555</v>
       </c>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="G520" s="10"/>
     </row>
-    <row r="521" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A521" s="10" t="s">
         <v>555</v>
       </c>
@@ -19962,7 +19962,7 @@
       </c>
       <c r="G521" s="10"/>
     </row>
-    <row r="522" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A522" s="10" t="s">
         <v>555</v>
       </c>
@@ -19983,7 +19983,7 @@
       </c>
       <c r="G522" s="10"/>
     </row>
-    <row r="523" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A523" s="10" t="s">
         <v>555</v>
       </c>
@@ -20004,7 +20004,7 @@
       </c>
       <c r="G523" s="10"/>
     </row>
-    <row r="524" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A524" s="10" t="s">
         <v>555</v>
       </c>
@@ -20025,7 +20025,7 @@
       </c>
       <c r="G524" s="10"/>
     </row>
-    <row r="525" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A525" s="10" t="s">
         <v>555</v>
       </c>
@@ -20046,7 +20046,7 @@
       </c>
       <c r="G525" s="10"/>
     </row>
-    <row r="526" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A526" s="10" t="s">
         <v>555</v>
       </c>
@@ -20088,7 +20088,7 @@
       </c>
       <c r="G527" s="10"/>
     </row>
-    <row r="528" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A528" s="10" t="s">
         <v>557</v>
       </c>
@@ -20109,7 +20109,7 @@
       </c>
       <c r="G528" s="10"/>
     </row>
-    <row r="529" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A529" s="10" t="s">
         <v>557</v>
       </c>
@@ -20262,7 +20262,7 @@
       </c>
       <c r="G535" s="10"/>
     </row>
-    <row r="536" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A536" s="10" t="s">
         <v>557</v>
       </c>
@@ -20283,7 +20283,7 @@
       </c>
       <c r="G536" s="10"/>
     </row>
-    <row r="537" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A537" s="10" t="s">
         <v>557</v>
       </c>
@@ -20306,7 +20306,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="538" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A538" s="10" t="s">
         <v>557</v>
       </c>
@@ -20329,7 +20329,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="539" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A539" s="10" t="s">
         <v>557</v>
       </c>
@@ -20352,7 +20352,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="540" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A540" s="10" t="s">
         <v>557</v>
       </c>
@@ -20373,7 +20373,7 @@
       </c>
       <c r="G540" s="10"/>
     </row>
-    <row r="541" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A541" s="10" t="s">
         <v>557</v>
       </c>
@@ -20396,7 +20396,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="542" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A542" s="10" t="s">
         <v>557</v>
       </c>
@@ -20419,7 +20419,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="543" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A543" s="10" t="s">
         <v>557</v>
       </c>
@@ -20440,7 +20440,7 @@
       </c>
       <c r="G543" s="10"/>
     </row>
-    <row r="544" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A544" s="10" t="s">
         <v>557</v>
       </c>
@@ -20461,7 +20461,7 @@
       </c>
       <c r="G544" s="10"/>
     </row>
-    <row r="545" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A545" s="10" t="s">
         <v>14</v>
       </c>
@@ -20484,7 +20484,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="546" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A546" s="10" t="s">
         <v>14</v>
       </c>
@@ -20507,7 +20507,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="547" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A547" s="10" t="s">
         <v>14</v>
       </c>
@@ -20528,7 +20528,7 @@
       </c>
       <c r="G547" s="10"/>
     </row>
-    <row r="548" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A548" s="10" t="s">
         <v>14</v>
       </c>
@@ -20549,7 +20549,7 @@
       </c>
       <c r="G548" s="10"/>
     </row>
-    <row r="549" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A549" s="10" t="s">
         <v>14</v>
       </c>
@@ -20570,7 +20570,7 @@
       </c>
       <c r="G549" s="10"/>
     </row>
-    <row r="550" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A550" s="10" t="s">
         <v>14</v>
       </c>
@@ -20593,7 +20593,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="551" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A551" s="10" t="s">
         <v>14</v>
       </c>
@@ -20616,7 +20616,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="552" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A552" s="10" t="s">
         <v>14</v>
       </c>
@@ -20637,7 +20637,7 @@
       </c>
       <c r="G552" s="10"/>
     </row>
-    <row r="553" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A553" s="10" t="s">
         <v>14</v>
       </c>
@@ -20660,7 +20660,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="554" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A554" s="10" t="s">
         <v>14</v>
       </c>
@@ -20681,7 +20681,7 @@
       </c>
       <c r="G554" s="10"/>
     </row>
-    <row r="555" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A555" s="10" t="s">
         <v>14</v>
       </c>
@@ -20702,7 +20702,7 @@
       </c>
       <c r="G555" s="10"/>
     </row>
-    <row r="556" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A556" s="10" t="s">
         <v>14</v>
       </c>
@@ -20723,7 +20723,7 @@
       </c>
       <c r="G556" s="10"/>
     </row>
-    <row r="557" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A557" s="10" t="s">
         <v>14</v>
       </c>
@@ -20767,7 +20767,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="559" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A559" s="10" t="s">
         <v>14</v>
       </c>
@@ -20790,7 +20790,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="560" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A560" s="10" t="s">
         <v>14</v>
       </c>
@@ -20834,7 +20834,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="562" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A562" s="10" t="s">
         <v>14</v>
       </c>
@@ -20857,7 +20857,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="563" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A563" s="10" t="s">
         <v>14</v>
       </c>
@@ -20878,7 +20878,7 @@
       </c>
       <c r="G563" s="10"/>
     </row>
-    <row r="564" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A564" s="10" t="s">
         <v>14</v>
       </c>
@@ -20899,7 +20899,7 @@
       </c>
       <c r="G564" s="10"/>
     </row>
-    <row r="565" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A565" s="10" t="s">
         <v>14</v>
       </c>
@@ -20922,7 +20922,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="566" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A566" s="10" t="s">
         <v>14</v>
       </c>
@@ -20945,7 +20945,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="567" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A567" s="10" t="s">
         <v>14</v>
       </c>
@@ -20966,7 +20966,7 @@
       </c>
       <c r="G567" s="10"/>
     </row>
-    <row r="568" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A568" s="10" t="s">
         <v>14</v>
       </c>
@@ -20989,7 +20989,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="569" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A569" s="10" t="s">
         <v>14</v>
       </c>
@@ -21012,7 +21012,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="570" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A570" s="10" t="s">
         <v>14</v>
       </c>
@@ -21033,7 +21033,7 @@
       </c>
       <c r="G570" s="10"/>
     </row>
-    <row r="571" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A571" s="10" t="s">
         <v>14</v>
       </c>
@@ -21054,7 +21054,7 @@
       </c>
       <c r="G571" s="10"/>
     </row>
-    <row r="572" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A572" s="10" t="s">
         <v>14</v>
       </c>
@@ -21075,7 +21075,7 @@
       </c>
       <c r="G572" s="10"/>
     </row>
-    <row r="573" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A573" s="10" t="s">
         <v>14</v>
       </c>
@@ -21096,7 +21096,7 @@
       </c>
       <c r="G573" s="10"/>
     </row>
-    <row r="574" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A574" s="10" t="s">
         <v>14</v>
       </c>
@@ -21119,7 +21119,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="575" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A575" s="10" t="s">
         <v>14</v>
       </c>
@@ -21142,7 +21142,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="576" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A576" s="10" t="s">
         <v>14</v>
       </c>
@@ -21163,7 +21163,7 @@
       </c>
       <c r="G576" s="10"/>
     </row>
-    <row r="577" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A577" s="10" t="s">
         <v>14</v>
       </c>
@@ -21184,7 +21184,7 @@
       </c>
       <c r="G577" s="10"/>
     </row>
-    <row r="578" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A578" s="10" t="s">
         <v>14</v>
       </c>
@@ -21207,7 +21207,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="579" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A579" s="10" t="s">
         <v>14</v>
       </c>
@@ -21230,7 +21230,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="580" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A580" s="10" t="s">
         <v>14</v>
       </c>
@@ -21251,7 +21251,7 @@
       </c>
       <c r="G580" s="10"/>
     </row>
-    <row r="581" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A581" s="10" t="s">
         <v>14</v>
       </c>
@@ -21272,7 +21272,7 @@
       </c>
       <c r="G581" s="10"/>
     </row>
-    <row r="582" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A582" s="10" t="s">
         <v>14</v>
       </c>
@@ -21293,7 +21293,7 @@
       </c>
       <c r="G582" s="10"/>
     </row>
-    <row r="583" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A583" s="10" t="s">
         <v>14</v>
       </c>
@@ -21316,7 +21316,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="584" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A584" s="10" t="s">
         <v>14</v>
       </c>
@@ -21339,7 +21339,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="585" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A585" s="10" t="s">
         <v>14</v>
       </c>
@@ -21360,7 +21360,7 @@
       </c>
       <c r="G585" s="10"/>
     </row>
-    <row r="586" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A586" s="10" t="s">
         <v>14</v>
       </c>
@@ -21383,7 +21383,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="587" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A587" s="10" t="s">
         <v>14</v>
       </c>
@@ -21406,7 +21406,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="588" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A588" s="10" t="s">
         <v>14</v>
       </c>
@@ -21427,7 +21427,7 @@
       </c>
       <c r="G588" s="10"/>
     </row>
-    <row r="589" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A589" s="10" t="s">
         <v>14</v>
       </c>
@@ -21448,7 +21448,7 @@
       </c>
       <c r="G589" s="10"/>
     </row>
-    <row r="590" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A590" s="10" t="s">
         <v>14</v>
       </c>
@@ -21469,7 +21469,7 @@
       </c>
       <c r="G590" s="10"/>
     </row>
-    <row r="591" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A591" s="10" t="s">
         <v>14</v>
       </c>
@@ -21490,7 +21490,7 @@
       </c>
       <c r="G591" s="10"/>
     </row>
-    <row r="592" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A592" s="10" t="s">
         <v>14</v>
       </c>
@@ -21511,7 +21511,7 @@
       </c>
       <c r="G592" s="10"/>
     </row>
-    <row r="593" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A593" s="10" t="s">
         <v>14</v>
       </c>
@@ -21532,7 +21532,7 @@
       </c>
       <c r="G593" s="10"/>
     </row>
-    <row r="594" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A594" s="10" t="s">
         <v>14</v>
       </c>
@@ -21553,7 +21553,7 @@
       </c>
       <c r="G594" s="10"/>
     </row>
-    <row r="595" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A595" s="10" t="s">
         <v>14</v>
       </c>
@@ -21574,7 +21574,7 @@
       </c>
       <c r="G595" s="10"/>
     </row>
-    <row r="596" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A596" s="10" t="s">
         <v>14</v>
       </c>
@@ -21595,7 +21595,7 @@
       </c>
       <c r="G596" s="10"/>
     </row>
-    <row r="597" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A597" s="10" t="s">
         <v>14</v>
       </c>
@@ -21616,7 +21616,7 @@
       </c>
       <c r="G597" s="10"/>
     </row>
-    <row r="598" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A598" s="10" t="s">
         <v>14</v>
       </c>
@@ -21639,7 +21639,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="599" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A599" s="10" t="s">
         <v>14</v>
       </c>
@@ -21662,7 +21662,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="600" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A600" s="10" t="s">
         <v>14</v>
       </c>
@@ -21685,7 +21685,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="601" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A601" s="10" t="s">
         <v>14</v>
       </c>
@@ -21708,7 +21708,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="602" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A602" s="10" t="s">
         <v>14</v>
       </c>
@@ -21729,7 +21729,7 @@
       </c>
       <c r="G602" s="10"/>
     </row>
-    <row r="603" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A603" s="10" t="s">
         <v>14</v>
       </c>
@@ -21750,7 +21750,7 @@
       </c>
       <c r="G603" s="10"/>
     </row>
-    <row r="604" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A604" s="10" t="s">
         <v>14</v>
       </c>
@@ -21771,7 +21771,7 @@
       </c>
       <c r="G604" s="10"/>
     </row>
-    <row r="605" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A605" s="10" t="s">
         <v>14</v>
       </c>
@@ -21794,7 +21794,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="606" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A606" s="10" t="s">
         <v>14</v>
       </c>
@@ -21817,7 +21817,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="607" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A607" s="10" t="s">
         <v>14</v>
       </c>
@@ -21838,7 +21838,7 @@
       </c>
       <c r="G607" s="10"/>
     </row>
-    <row r="608" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A608" s="10" t="s">
         <v>14</v>
       </c>
@@ -21859,7 +21859,7 @@
       </c>
       <c r="G608" s="10"/>
     </row>
-    <row r="609" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A609" s="10" t="s">
         <v>14</v>
       </c>
@@ -21882,7 +21882,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="610" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A610" s="10" t="s">
         <v>14</v>
       </c>
@@ -21905,7 +21905,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="611" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A611" s="10" t="s">
         <v>14</v>
       </c>
@@ -21926,7 +21926,7 @@
       </c>
       <c r="G611" s="10"/>
     </row>
-    <row r="612" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A612" s="10" t="s">
         <v>14</v>
       </c>
@@ -21947,7 +21947,7 @@
       </c>
       <c r="G612" s="10"/>
     </row>
-    <row r="613" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A613" s="10" t="s">
         <v>14</v>
       </c>
@@ -21968,7 +21968,7 @@
       </c>
       <c r="G613" s="10"/>
     </row>
-    <row r="614" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A614" s="10" t="s">
         <v>14</v>
       </c>
@@ -21991,7 +21991,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="615" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A615" s="10" t="s">
         <v>14</v>
       </c>
@@ -22014,7 +22014,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="616" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A616" s="10" t="s">
         <v>14</v>
       </c>
@@ -22037,7 +22037,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="617" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A617" s="10" t="s">
         <v>14</v>
       </c>
@@ -22060,7 +22060,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="618" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A618" s="10" t="s">
         <v>14</v>
       </c>
@@ -22081,7 +22081,7 @@
       </c>
       <c r="G618" s="10"/>
     </row>
-    <row r="619" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A619" s="10" t="s">
         <v>14</v>
       </c>
@@ -22102,7 +22102,7 @@
       </c>
       <c r="G619" s="10"/>
     </row>
-    <row r="620" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A620" s="10" t="s">
         <v>14</v>
       </c>
@@ -22125,7 +22125,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="621" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A621" s="10" t="s">
         <v>14</v>
       </c>
@@ -22148,7 +22148,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="622" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A622" s="10" t="s">
         <v>14</v>
       </c>
@@ -22171,7 +22171,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="623" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A623" s="10" t="s">
         <v>14</v>
       </c>
@@ -22194,7 +22194,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="624" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A624" s="10" t="s">
         <v>14</v>
       </c>
@@ -22217,7 +22217,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="625" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A625" s="10" t="s">
         <v>14</v>
       </c>
@@ -22240,7 +22240,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="626" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A626" s="10" t="s">
         <v>14</v>
       </c>
@@ -22263,7 +22263,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="627" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A627" s="10" t="s">
         <v>14</v>
       </c>
@@ -22286,7 +22286,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="628" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A628" s="10" t="s">
         <v>14</v>
       </c>
@@ -22309,7 +22309,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="629" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A629" s="10" t="s">
         <v>14</v>
       </c>
@@ -22330,7 +22330,7 @@
       </c>
       <c r="G629" s="10"/>
     </row>
-    <row r="630" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A630" s="10" t="s">
         <v>14</v>
       </c>
@@ -22351,7 +22351,7 @@
       </c>
       <c r="G630" s="10"/>
     </row>
-    <row r="631" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A631" s="10" t="s">
         <v>14</v>
       </c>
@@ -22374,7 +22374,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="632" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A632" s="10" t="s">
         <v>14</v>
       </c>
@@ -22397,7 +22397,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="633" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A633" s="10" t="s">
         <v>14</v>
       </c>
@@ -22420,7 +22420,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="634" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A634" s="10" t="s">
         <v>14</v>
       </c>
@@ -22443,7 +22443,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="635" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A635" s="10" t="s">
         <v>14</v>
       </c>
@@ -22464,7 +22464,7 @@
       </c>
       <c r="G635" s="10"/>
     </row>
-    <row r="636" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A636" s="10" t="s">
         <v>14</v>
       </c>
@@ -22485,7 +22485,7 @@
       </c>
       <c r="G636" s="10"/>
     </row>
-    <row r="637" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A637" s="10" t="s">
         <v>14</v>
       </c>
@@ -22506,7 +22506,7 @@
       </c>
       <c r="G637" s="10"/>
     </row>
-    <row r="638" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A638" s="10" t="s">
         <v>14</v>
       </c>
@@ -22527,7 +22527,7 @@
       </c>
       <c r="G638" s="10"/>
     </row>
-    <row r="639" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A639" s="10" t="s">
         <v>14</v>
       </c>
@@ -22550,7 +22550,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="640" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A640" s="10" t="s">
         <v>14</v>
       </c>
@@ -22573,7 +22573,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="641" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A641" s="10" t="s">
         <v>14</v>
       </c>
@@ -22596,7 +22596,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="642" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A642" s="10" t="s">
         <v>14</v>
       </c>
@@ -22619,7 +22619,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="643" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A643" s="10" t="s">
         <v>14</v>
       </c>
@@ -22640,7 +22640,7 @@
       </c>
       <c r="G643" s="10"/>
     </row>
-    <row r="644" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A644" s="10" t="s">
         <v>14</v>
       </c>
@@ -22661,7 +22661,7 @@
       </c>
       <c r="G644" s="10"/>
     </row>
-    <row r="645" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A645" s="10" t="s">
         <v>14</v>
       </c>
@@ -22682,7 +22682,7 @@
       </c>
       <c r="G645" s="10"/>
     </row>
-    <row r="646" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A646" s="10" t="s">
         <v>14</v>
       </c>
@@ -22703,7 +22703,7 @@
       </c>
       <c r="G646" s="10"/>
     </row>
-    <row r="647" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A647" s="10" t="s">
         <v>14</v>
       </c>
@@ -22724,7 +22724,7 @@
       </c>
       <c r="G647" s="10"/>
     </row>
-    <row r="648" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A648" s="10" t="s">
         <v>14</v>
       </c>
@@ -22747,7 +22747,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="649" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A649" s="10" t="s">
         <v>14</v>
       </c>
@@ -22770,7 +22770,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="650" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A650" s="10" t="s">
         <v>14</v>
       </c>
@@ -22791,7 +22791,7 @@
       </c>
       <c r="G650" s="10"/>
     </row>
-    <row r="651" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A651" s="10" t="s">
         <v>14</v>
       </c>
@@ -22814,7 +22814,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="652" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A652" s="10" t="s">
         <v>14</v>
       </c>
@@ -22837,7 +22837,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="653" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A653" s="10" t="s">
         <v>14</v>
       </c>
@@ -22858,7 +22858,7 @@
       </c>
       <c r="G653" s="10"/>
     </row>
-    <row r="654" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A654" s="10" t="s">
         <v>14</v>
       </c>
@@ -22879,7 +22879,7 @@
       </c>
       <c r="G654" s="10"/>
     </row>
-    <row r="655" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A655" s="10" t="s">
         <v>14</v>
       </c>
@@ -22900,7 +22900,7 @@
       </c>
       <c r="G655" s="10"/>
     </row>
-    <row r="656" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A656" s="10" t="s">
         <v>14</v>
       </c>
@@ -22923,7 +22923,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="657" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A657" s="10" t="s">
         <v>14</v>
       </c>
@@ -22946,7 +22946,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="658" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A658" s="10" t="s">
         <v>14</v>
       </c>
@@ -22967,7 +22967,7 @@
       </c>
       <c r="G658" s="10"/>
     </row>
-    <row r="659" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A659" s="10" t="s">
         <v>14</v>
       </c>
@@ -22990,7 +22990,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="660" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A660" s="10" t="s">
         <v>14</v>
       </c>
@@ -23013,7 +23013,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="661" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A661" s="10" t="s">
         <v>14</v>
       </c>
@@ -23034,7 +23034,7 @@
       </c>
       <c r="G661" s="10"/>
     </row>
-    <row r="662" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A662" s="10" t="s">
         <v>14</v>
       </c>
@@ -23055,7 +23055,7 @@
       </c>
       <c r="G662" s="10"/>
     </row>
-    <row r="663" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A663" s="10" t="s">
         <v>14</v>
       </c>
@@ -23076,7 +23076,7 @@
       </c>
       <c r="G663" s="10"/>
     </row>
-    <row r="664" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A664" s="10" t="s">
         <v>14</v>
       </c>
@@ -23097,7 +23097,7 @@
       </c>
       <c r="G664" s="10"/>
     </row>
-    <row r="665" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A665" s="10" t="s">
         <v>14</v>
       </c>
@@ -23118,7 +23118,7 @@
       </c>
       <c r="G665" s="10"/>
     </row>
-    <row r="666" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A666" s="10" t="s">
         <v>14</v>
       </c>
@@ -23139,7 +23139,7 @@
       </c>
       <c r="G666" s="10"/>
     </row>
-    <row r="667" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A667" s="10" t="s">
         <v>14</v>
       </c>
@@ -23162,7 +23162,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="668" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A668" s="10" t="s">
         <v>14</v>
       </c>
@@ -23206,7 +23206,7 @@
       </c>
       <c r="G669" s="10"/>
     </row>
-    <row r="670" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A670" s="10" t="s">
         <v>14</v>
       </c>
@@ -23227,7 +23227,7 @@
       </c>
       <c r="G670" s="10"/>
     </row>
-    <row r="671" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A671" s="10" t="s">
         <v>14</v>
       </c>
@@ -23250,7 +23250,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="672" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A672" s="10" t="s">
         <v>14</v>
       </c>
@@ -23273,7 +23273,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="673" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A673" s="10" t="s">
         <v>14</v>
       </c>
@@ -23294,7 +23294,7 @@
       </c>
       <c r="G673" s="10"/>
     </row>
-    <row r="674" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A674" s="10" t="s">
         <v>14</v>
       </c>
@@ -23317,7 +23317,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="675" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A675" s="10" t="s">
         <v>14</v>
       </c>
@@ -23340,7 +23340,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="676" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A676" s="10" t="s">
         <v>14</v>
       </c>
@@ -23384,7 +23384,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="678" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A678" s="10" t="s">
         <v>14</v>
       </c>
@@ -23407,7 +23407,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="679" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A679" s="10" t="s">
         <v>14</v>
       </c>
@@ -23428,7 +23428,7 @@
       </c>
       <c r="G679" s="10"/>
     </row>
-    <row r="680" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A680" s="10" t="s">
         <v>14</v>
       </c>
@@ -23449,7 +23449,7 @@
       </c>
       <c r="G680" s="10"/>
     </row>
-    <row r="681" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A681" s="10" t="s">
         <v>14</v>
       </c>
@@ -23470,7 +23470,7 @@
       </c>
       <c r="G681" s="10"/>
     </row>
-    <row r="682" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A682" s="10" t="s">
         <v>14</v>
       </c>
@@ -23493,7 +23493,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="683" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A683" s="10" t="s">
         <v>14</v>
       </c>
@@ -23516,7 +23516,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="684" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A684" s="10" t="s">
         <v>14</v>
       </c>
@@ -23539,7 +23539,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="685" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A685" s="10" t="s">
         <v>14</v>
       </c>
@@ -23562,7 +23562,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="686" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A686" s="10" t="s">
         <v>14</v>
       </c>
@@ -23583,7 +23583,7 @@
       </c>
       <c r="G686" s="10"/>
     </row>
-    <row r="687" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A687" s="10" t="s">
         <v>14</v>
       </c>
@@ -23604,7 +23604,7 @@
       </c>
       <c r="G687" s="10"/>
     </row>
-    <row r="688" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A688" s="10" t="s">
         <v>14</v>
       </c>
@@ -23625,7 +23625,7 @@
       </c>
       <c r="G688" s="10"/>
     </row>
-    <row r="689" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A689" s="10" t="s">
         <v>14</v>
       </c>
@@ -23646,7 +23646,7 @@
       </c>
       <c r="G689" s="10"/>
     </row>
-    <row r="690" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A690" s="10" t="s">
         <v>14</v>
       </c>
@@ -23669,7 +23669,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="691" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A691" s="10" t="s">
         <v>14</v>
       </c>
@@ -23692,7 +23692,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="692" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A692" s="10" t="s">
         <v>14</v>
       </c>
@@ -23736,7 +23736,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="694" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A694" s="10" t="s">
         <v>14</v>
       </c>
@@ -23759,7 +23759,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="695" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A695" s="10" t="s">
         <v>14</v>
       </c>
@@ -23780,7 +23780,7 @@
       </c>
       <c r="G695" s="10"/>
     </row>
-    <row r="696" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A696" s="10" t="s">
         <v>14</v>
       </c>
@@ -23801,7 +23801,7 @@
       </c>
       <c r="G696" s="10"/>
     </row>
-    <row r="697" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A697" s="10" t="s">
         <v>14</v>
       </c>
@@ -23822,7 +23822,7 @@
       </c>
       <c r="G697" s="10"/>
     </row>
-    <row r="698" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A698" s="10" t="s">
         <v>14</v>
       </c>
@@ -23843,7 +23843,7 @@
       </c>
       <c r="G698" s="10"/>
     </row>
-    <row r="699" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A699" s="10" t="s">
         <v>14</v>
       </c>
@@ -23864,7 +23864,7 @@
       </c>
       <c r="G699" s="10"/>
     </row>
-    <row r="700" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A700" s="10" t="s">
         <v>14</v>
       </c>
@@ -23885,7 +23885,7 @@
       </c>
       <c r="G700" s="10"/>
     </row>
-    <row r="701" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A701" s="10" t="s">
         <v>14</v>
       </c>
@@ -23906,7 +23906,7 @@
       </c>
       <c r="G701" s="10"/>
     </row>
-    <row r="702" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A702" s="10" t="s">
         <v>14</v>
       </c>
@@ -23929,7 +23929,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="703" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A703" s="10" t="s">
         <v>14</v>
       </c>
@@ -23952,7 +23952,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="704" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A704" s="10" t="s">
         <v>14</v>
       </c>
@@ -23973,7 +23973,7 @@
       </c>
       <c r="G704" s="10"/>
     </row>
-    <row r="705" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A705" s="10" t="s">
         <v>14</v>
       </c>
@@ -23996,7 +23996,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="706" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A706" s="10" t="s">
         <v>14</v>
       </c>
@@ -24019,7 +24019,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="707" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A707" s="10" t="s">
         <v>14</v>
       </c>
@@ -24040,7 +24040,7 @@
       </c>
       <c r="G707" s="10"/>
     </row>
-    <row r="708" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A708" s="10" t="s">
         <v>14</v>
       </c>
@@ -24061,7 +24061,7 @@
       </c>
       <c r="G708" s="10"/>
     </row>
-    <row r="709" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A709" s="10" t="s">
         <v>14</v>
       </c>
@@ -24082,7 +24082,7 @@
       </c>
       <c r="G709" s="10"/>
     </row>
-    <row r="710" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A710" s="10" t="s">
         <v>14</v>
       </c>
@@ -24103,7 +24103,7 @@
       </c>
       <c r="G710" s="10"/>
     </row>
-    <row r="711" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A711" s="10" t="s">
         <v>399</v>
       </c>
@@ -24123,7 +24123,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="712" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A712" s="10" t="s">
         <v>399</v>
       </c>
@@ -24143,7 +24143,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="713" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="713" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A713" s="10" t="s">
         <v>399</v>
       </c>
@@ -24163,7 +24163,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="714" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A714" s="10" t="s">
         <v>399</v>
       </c>
@@ -24185,6 +24185,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G714" xr:uid="{B85857DA-147B-4693-A73B-69F8E49F4406}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="-"/>
+        <filter val="0"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G24">
       <sortCondition ref="C1:C714"/>
     </sortState>

--- a/data/MI/Penelope/SupplementaryData1_Calculation_Metal_Demand.xlsx
+++ b/data/MI/Penelope/SupplementaryData1_Calculation_Metal_Demand.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{B39B6A3F-D26A-48B9-A17C-949B8561B238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43DA72F2-0C90-4D5A-B61A-0121A95940BF}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="-23595" yWindow="4260" windowWidth="14400" windowHeight="7275" firstSheet="10" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-705" windowWidth="29040" windowHeight="15720" firstSheet="9" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table of content" sheetId="26" r:id="rId1"/>
@@ -3384,24 +3384,6 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3409,6 +3391,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3432,25 +3423,40 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3474,13 +3480,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3489,22 +3489,22 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -24665,10 +24665,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="263" t="s">
+      <c r="A2" s="260" t="s">
         <v>363</v>
       </c>
-      <c r="B2" s="263"/>
+      <c r="B2" s="260"/>
       <c r="C2" s="141" t="s">
         <v>342</v>
       </c>
@@ -24680,10 +24680,10 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="255" t="s">
+      <c r="A3" s="268" t="s">
         <v>366</v>
       </c>
-      <c r="B3" s="255"/>
+      <c r="B3" s="268"/>
       <c r="C3" s="141" t="s">
         <v>348</v>
       </c>
@@ -24695,8 +24695,8 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="255"/>
-      <c r="B4" s="255"/>
+      <c r="A4" s="268"/>
+      <c r="B4" s="268"/>
       <c r="C4" s="142" t="s">
         <v>342</v>
       </c>
@@ -24708,8 +24708,8 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="255"/>
-      <c r="B5" s="255"/>
+      <c r="A5" s="268"/>
+      <c r="B5" s="268"/>
       <c r="C5" s="142" t="s">
         <v>349</v>
       </c>
@@ -24721,8 +24721,8 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="255"/>
-      <c r="B6" s="255"/>
+      <c r="A6" s="268"/>
+      <c r="B6" s="268"/>
       <c r="C6" s="142" t="s">
         <v>352</v>
       </c>
@@ -24734,8 +24734,8 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="255"/>
-      <c r="B7" s="255"/>
+      <c r="A7" s="268"/>
+      <c r="B7" s="268"/>
       <c r="C7" s="143" t="s">
         <v>350</v>
       </c>
@@ -24747,10 +24747,10 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="263" t="s">
+      <c r="A8" s="260" t="s">
         <v>368</v>
       </c>
-      <c r="B8" s="263"/>
+      <c r="B8" s="260"/>
       <c r="C8" s="144" t="s">
         <v>360</v>
       </c>
@@ -24762,7 +24762,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="261" t="s">
+      <c r="A9" s="255" t="s">
         <v>272</v>
       </c>
       <c r="B9" s="145" t="s">
@@ -24779,7 +24779,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="261"/>
+      <c r="A10" s="255"/>
       <c r="B10" s="145" t="s">
         <v>326</v>
       </c>
@@ -24794,8 +24794,8 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="261"/>
-      <c r="B11" s="260" t="s">
+      <c r="A11" s="255"/>
+      <c r="B11" s="254" t="s">
         <v>329</v>
       </c>
       <c r="C11" s="38" t="s">
@@ -24804,26 +24804,26 @@
       <c r="D11" s="201" t="s">
         <v>331</v>
       </c>
-      <c r="E11" s="254" t="s">
+      <c r="E11" s="267" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="261"/>
-      <c r="B12" s="260"/>
+      <c r="A12" s="255"/>
+      <c r="B12" s="254"/>
       <c r="C12" s="38" t="s">
         <v>333</v>
       </c>
       <c r="D12" s="201" t="s">
         <v>573</v>
       </c>
-      <c r="E12" s="254"/>
+      <c r="E12" s="267"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="261" t="s">
+      <c r="A13" s="255" t="s">
         <v>276</v>
       </c>
-      <c r="B13" s="261"/>
+      <c r="B13" s="255"/>
       <c r="C13" s="38" t="s">
         <v>243</v>
       </c>
@@ -24835,10 +24835,10 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="261" t="s">
+      <c r="A14" s="255" t="s">
         <v>278</v>
       </c>
-      <c r="B14" s="261"/>
+      <c r="B14" s="255"/>
       <c r="C14" s="38" t="s">
         <v>243</v>
       </c>
@@ -24850,10 +24850,10 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="264" t="s">
+      <c r="A15" s="261" t="s">
         <v>334</v>
       </c>
-      <c r="B15" s="265"/>
+      <c r="B15" s="262"/>
       <c r="C15" s="142" t="s">
         <v>135</v>
       </c>
@@ -24865,8 +24865,8 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="266"/>
-      <c r="B16" s="267"/>
+      <c r="A16" s="263"/>
+      <c r="B16" s="264"/>
       <c r="C16" s="142" t="s">
         <v>136</v>
       </c>
@@ -24878,10 +24878,10 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="259" t="s">
+      <c r="A17" s="269" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="259"/>
+      <c r="B17" s="269"/>
       <c r="C17" s="44" t="s">
         <v>64</v>
       </c>
@@ -24893,8 +24893,8 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="259"/>
-      <c r="B18" s="259"/>
+      <c r="A18" s="269"/>
+      <c r="B18" s="269"/>
       <c r="C18" s="45" t="s">
         <v>24</v>
       </c>
@@ -24906,8 +24906,8 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="259"/>
-      <c r="B19" s="259"/>
+      <c r="A19" s="269"/>
+      <c r="B19" s="269"/>
       <c r="C19" s="45" t="s">
         <v>65</v>
       </c>
@@ -24919,8 +24919,8 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="259"/>
-      <c r="B20" s="259"/>
+      <c r="A20" s="269"/>
+      <c r="B20" s="269"/>
       <c r="C20" s="44" t="s">
         <v>66</v>
       </c>
@@ -24932,8 +24932,8 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="259"/>
-      <c r="B21" s="259"/>
+      <c r="A21" s="269"/>
+      <c r="B21" s="269"/>
       <c r="C21" s="45" t="s">
         <v>67</v>
       </c>
@@ -24975,10 +24975,10 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" s="268" t="s">
+      <c r="A24" s="265" t="s">
         <v>280</v>
       </c>
-      <c r="B24" s="256" t="s">
+      <c r="B24" s="258" t="s">
         <v>337</v>
       </c>
       <c r="C24" s="38" t="s">
@@ -24992,8 +24992,8 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" s="269"/>
-      <c r="B25" s="257"/>
+      <c r="A25" s="266"/>
+      <c r="B25" s="259"/>
       <c r="C25" s="38" t="s">
         <v>269</v>
       </c>
@@ -25005,8 +25005,8 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" s="269"/>
-      <c r="B26" s="258" t="s">
+      <c r="A26" s="266"/>
+      <c r="B26" s="257" t="s">
         <v>318</v>
       </c>
       <c r="C26" s="175" t="s">
@@ -25020,8 +25020,8 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" s="269"/>
-      <c r="B27" s="256"/>
+      <c r="A27" s="266"/>
+      <c r="B27" s="258"/>
       <c r="C27" s="10" t="s">
         <v>522</v>
       </c>
@@ -25031,8 +25031,8 @@
       <c r="E27" s="123"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" s="269"/>
-      <c r="B28" s="256"/>
+      <c r="A28" s="266"/>
+      <c r="B28" s="258"/>
       <c r="C28" s="175" t="s">
         <v>518</v>
       </c>
@@ -25042,8 +25042,8 @@
       <c r="E28" s="123"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" s="269"/>
-      <c r="B29" s="257"/>
+      <c r="A29" s="266"/>
+      <c r="B29" s="259"/>
       <c r="C29" s="10" t="s">
         <v>521</v>
       </c>
@@ -25055,8 +25055,8 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="269"/>
-      <c r="B30" s="258" t="s">
+      <c r="A30" s="266"/>
+      <c r="B30" s="257" t="s">
         <v>322</v>
       </c>
       <c r="C30" s="38" t="s">
@@ -25070,8 +25070,8 @@
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" s="269"/>
-      <c r="B31" s="256"/>
+      <c r="A31" s="266"/>
+      <c r="B31" s="258"/>
       <c r="C31" s="38" t="s">
         <v>256</v>
       </c>
@@ -25083,8 +25083,8 @@
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A32" s="269"/>
-      <c r="B32" s="256"/>
+      <c r="A32" s="266"/>
+      <c r="B32" s="258"/>
       <c r="C32" s="38" t="s">
         <v>258</v>
       </c>
@@ -25096,8 +25096,8 @@
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A33" s="269"/>
-      <c r="B33" s="257"/>
+      <c r="A33" s="266"/>
+      <c r="B33" s="259"/>
       <c r="C33" s="10" t="s">
         <v>521</v>
       </c>
@@ -25107,8 +25107,8 @@
       <c r="E33" s="123"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A34" s="269"/>
-      <c r="B34" s="258" t="s">
+      <c r="A34" s="266"/>
+      <c r="B34" s="257" t="s">
         <v>612</v>
       </c>
       <c r="C34" s="38" t="s">
@@ -25123,7 +25123,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="174"/>
-      <c r="B35" s="256"/>
+      <c r="B35" s="258"/>
       <c r="C35" s="38" t="s">
         <v>476</v>
       </c>
@@ -25136,7 +25136,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="174"/>
-      <c r="B36" s="256"/>
+      <c r="B36" s="258"/>
       <c r="C36" s="38" t="s">
         <v>478</v>
       </c>
@@ -25149,7 +25149,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="174"/>
-      <c r="B37" s="256"/>
+      <c r="B37" s="258"/>
       <c r="C37" s="38" t="s">
         <v>480</v>
       </c>
@@ -25162,7 +25162,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="174"/>
-      <c r="B38" s="257"/>
+      <c r="B38" s="259"/>
       <c r="C38" s="199" t="s">
         <v>484</v>
       </c>
@@ -25174,10 +25174,10 @@
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A39" s="262" t="s">
+      <c r="A39" s="256" t="s">
         <v>336</v>
       </c>
-      <c r="B39" s="262"/>
+      <c r="B39" s="256"/>
       <c r="C39" s="38" t="s">
         <v>592</v>
       </c>
@@ -25189,8 +25189,8 @@
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A40" s="262"/>
-      <c r="B40" s="262"/>
+      <c r="A40" s="256"/>
+      <c r="B40" s="256"/>
       <c r="C40" s="41" t="s">
         <v>24</v>
       </c>
@@ -25202,8 +25202,8 @@
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A41" s="262"/>
-      <c r="B41" s="262"/>
+      <c r="A41" s="256"/>
+      <c r="B41" s="256"/>
       <c r="C41" s="38" t="s">
         <v>594</v>
       </c>
@@ -25215,8 +25215,8 @@
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A42" s="262"/>
-      <c r="B42" s="262"/>
+      <c r="A42" s="256"/>
+      <c r="B42" s="256"/>
       <c r="C42" s="38" t="s">
         <v>590</v>
       </c>
@@ -25228,8 +25228,8 @@
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A43" s="262"/>
-      <c r="B43" s="262"/>
+      <c r="A43" s="256"/>
+      <c r="B43" s="256"/>
       <c r="C43" s="38" t="s">
         <v>607</v>
       </c>
@@ -25241,8 +25241,8 @@
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A44" s="262"/>
-      <c r="B44" s="262"/>
+      <c r="A44" s="256"/>
+      <c r="B44" s="256"/>
       <c r="C44" s="38" t="s">
         <v>30</v>
       </c>
@@ -25254,8 +25254,8 @@
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A45" s="262"/>
-      <c r="B45" s="262"/>
+      <c r="A45" s="256"/>
+      <c r="B45" s="256"/>
       <c r="C45" s="39" t="s">
         <v>595</v>
       </c>
@@ -25267,8 +25267,8 @@
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A46" s="262"/>
-      <c r="B46" s="262"/>
+      <c r="A46" s="256"/>
+      <c r="B46" s="256"/>
       <c r="C46" s="10" t="s">
         <v>597</v>
       </c>
@@ -25280,8 +25280,8 @@
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A47" s="262"/>
-      <c r="B47" s="262"/>
+      <c r="A47" s="256"/>
+      <c r="B47" s="256"/>
       <c r="C47" s="38" t="s">
         <v>33</v>
       </c>
@@ -25293,8 +25293,8 @@
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A48" s="262"/>
-      <c r="B48" s="262"/>
+      <c r="A48" s="256"/>
+      <c r="B48" s="256"/>
       <c r="C48" s="38" t="s">
         <v>25</v>
       </c>
@@ -25306,8 +25306,8 @@
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A49" s="262"/>
-      <c r="B49" s="262"/>
+      <c r="A49" s="256"/>
+      <c r="B49" s="256"/>
       <c r="C49" s="38" t="s">
         <v>599</v>
       </c>
@@ -25319,8 +25319,8 @@
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A50" s="262"/>
-      <c r="B50" s="262"/>
+      <c r="A50" s="256"/>
+      <c r="B50" s="256"/>
       <c r="C50" s="38" t="s">
         <v>600</v>
       </c>
@@ -25332,8 +25332,8 @@
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A51" s="262"/>
-      <c r="B51" s="262"/>
+      <c r="A51" s="256"/>
+      <c r="B51" s="256"/>
       <c r="C51" s="42" t="s">
         <v>27</v>
       </c>
@@ -25345,8 +25345,8 @@
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A52" s="262"/>
-      <c r="B52" s="262"/>
+      <c r="A52" s="256"/>
+      <c r="B52" s="256"/>
       <c r="C52" s="38" t="s">
         <v>470</v>
       </c>
@@ -25358,8 +25358,8 @@
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A53" s="262"/>
-      <c r="B53" s="262"/>
+      <c r="A53" s="256"/>
+      <c r="B53" s="256"/>
       <c r="C53" s="38" t="s">
         <v>31</v>
       </c>
@@ -25371,8 +25371,8 @@
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A54" s="262"/>
-      <c r="B54" s="262"/>
+      <c r="A54" s="256"/>
+      <c r="B54" s="256"/>
       <c r="C54" s="38" t="s">
         <v>603</v>
       </c>
@@ -25384,8 +25384,8 @@
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A55" s="262"/>
-      <c r="B55" s="262"/>
+      <c r="A55" s="256"/>
+      <c r="B55" s="256"/>
       <c r="C55" s="38" t="s">
         <v>36</v>
       </c>
@@ -25397,8 +25397,8 @@
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A56" s="262"/>
-      <c r="B56" s="262"/>
+      <c r="A56" s="256"/>
+      <c r="B56" s="256"/>
       <c r="C56" s="38" t="s">
         <v>38</v>
       </c>
@@ -25410,8 +25410,8 @@
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A57" s="262"/>
-      <c r="B57" s="262"/>
+      <c r="A57" s="256"/>
+      <c r="B57" s="256"/>
       <c r="C57" s="38" t="s">
         <v>605</v>
       </c>
@@ -25423,8 +25423,8 @@
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A58" s="262"/>
-      <c r="B58" s="262"/>
+      <c r="A58" s="256"/>
+      <c r="B58" s="256"/>
       <c r="C58" s="38" t="s">
         <v>589</v>
       </c>
@@ -25436,8 +25436,8 @@
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A59" s="262"/>
-      <c r="B59" s="262"/>
+      <c r="A59" s="256"/>
+      <c r="B59" s="256"/>
       <c r="C59" s="10" t="s">
         <v>565</v>
       </c>
@@ -25446,8 +25446,8 @@
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A60" s="262"/>
-      <c r="B60" s="262"/>
+      <c r="A60" s="256"/>
+      <c r="B60" s="256"/>
       <c r="C60" s="39" t="s">
         <v>26</v>
       </c>
@@ -25456,8 +25456,8 @@
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A61" s="262"/>
-      <c r="B61" s="262"/>
+      <c r="A61" s="256"/>
+      <c r="B61" s="256"/>
       <c r="C61" s="40" t="s">
         <v>23</v>
       </c>
@@ -25466,8 +25466,8 @@
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A62" s="262"/>
-      <c r="B62" s="262"/>
+      <c r="A62" s="256"/>
+      <c r="B62" s="256"/>
       <c r="C62" s="38" t="s">
         <v>506</v>
       </c>
@@ -25614,6 +25614,12 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="A3:B7"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="A17:B21"/>
+    <mergeCell ref="A22:B22"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="A13:B13"/>
@@ -25627,12 +25633,6 @@
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A24:A34"/>
     <mergeCell ref="B34:B38"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="A3:B7"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="A17:B21"/>
-    <mergeCell ref="A22:B22"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D19" r:id="rId1" display="https://doi.org/10.1016/j.apenergy.2017.05.151" xr:uid="{18C3015B-E60F-4C34-906E-66D664152807}"/>
@@ -25670,59 +25670,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.35">
-      <c r="A1" s="273" t="s">
+      <c r="A1" s="278" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="273"/>
-      <c r="C1" s="273"/>
+      <c r="B1" s="278"/>
+      <c r="C1" s="278"/>
     </row>
     <row r="2" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="274" t="s">
+      <c r="A3" s="292" t="s">
         <v>140</v>
       </c>
-      <c r="B3" s="275"/>
-      <c r="C3" s="275"/>
-      <c r="D3" s="275"/>
-      <c r="E3" s="275"/>
-      <c r="F3" s="275"/>
-      <c r="G3" s="275"/>
-      <c r="H3" s="275"/>
-      <c r="I3" s="275"/>
-      <c r="J3" s="275"/>
-      <c r="K3" s="275"/>
-      <c r="L3" s="275"/>
-      <c r="M3" s="275"/>
-      <c r="N3" s="275"/>
-      <c r="O3" s="275"/>
-      <c r="P3" s="276"/>
-      <c r="R3" s="277" t="s">
+      <c r="B3" s="293"/>
+      <c r="C3" s="293"/>
+      <c r="D3" s="293"/>
+      <c r="E3" s="293"/>
+      <c r="F3" s="293"/>
+      <c r="G3" s="293"/>
+      <c r="H3" s="293"/>
+      <c r="I3" s="293"/>
+      <c r="J3" s="293"/>
+      <c r="K3" s="293"/>
+      <c r="L3" s="293"/>
+      <c r="M3" s="293"/>
+      <c r="N3" s="293"/>
+      <c r="O3" s="293"/>
+      <c r="P3" s="294"/>
+      <c r="R3" s="279" t="s">
         <v>141</v>
       </c>
-      <c r="S3" s="278"/>
-      <c r="T3" s="278"/>
-      <c r="U3" s="278"/>
-      <c r="V3" s="278"/>
-      <c r="W3" s="278"/>
-      <c r="X3" s="278"/>
-      <c r="Y3" s="278"/>
-      <c r="Z3" s="278"/>
-      <c r="AA3" s="278"/>
-      <c r="AB3" s="278"/>
-      <c r="AC3" s="278"/>
-      <c r="AD3" s="278"/>
-      <c r="AE3" s="278"/>
-      <c r="AF3" s="278"/>
-      <c r="AG3" s="279"/>
-      <c r="AI3" s="280" t="s">
+      <c r="S3" s="280"/>
+      <c r="T3" s="280"/>
+      <c r="U3" s="280"/>
+      <c r="V3" s="280"/>
+      <c r="W3" s="280"/>
+      <c r="X3" s="280"/>
+      <c r="Y3" s="280"/>
+      <c r="Z3" s="280"/>
+      <c r="AA3" s="280"/>
+      <c r="AB3" s="280"/>
+      <c r="AC3" s="280"/>
+      <c r="AD3" s="280"/>
+      <c r="AE3" s="280"/>
+      <c r="AF3" s="280"/>
+      <c r="AG3" s="281"/>
+      <c r="AI3" s="282" t="s">
         <v>142</v>
       </c>
-      <c r="AJ3" s="281"/>
-      <c r="AK3" s="281"/>
-      <c r="AL3" s="281"/>
-      <c r="AM3" s="281"/>
-      <c r="AN3" s="281"/>
-      <c r="AO3" s="282"/>
+      <c r="AJ3" s="283"/>
+      <c r="AK3" s="283"/>
+      <c r="AL3" s="283"/>
+      <c r="AM3" s="283"/>
+      <c r="AN3" s="283"/>
+      <c r="AO3" s="284"/>
     </row>
     <row r="4" spans="1:41" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="58" t="s">
@@ -25773,12 +25773,12 @@
     </row>
     <row r="5" spans="1:41" x14ac:dyDescent="0.35">
       <c r="B5" s="1"/>
-      <c r="C5" s="284" t="s">
+      <c r="C5" s="273" t="s">
         <v>143</v>
       </c>
-      <c r="D5" s="285"/>
-      <c r="E5" s="285"/>
-      <c r="F5" s="286"/>
+      <c r="D5" s="286"/>
+      <c r="E5" s="286"/>
+      <c r="F5" s="274"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
         <v>144</v>
@@ -26170,12 +26170,12 @@
     <row r="12" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A12" s="65"/>
       <c r="B12" s="1"/>
-      <c r="C12" s="284" t="s">
+      <c r="C12" s="273" t="s">
         <v>154</v>
       </c>
-      <c r="D12" s="285"/>
-      <c r="E12" s="285"/>
-      <c r="F12" s="286"/>
+      <c r="D12" s="286"/>
+      <c r="E12" s="286"/>
+      <c r="F12" s="274"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -26298,12 +26298,12 @@
       <c r="P14" s="61"/>
       <c r="R14" s="65"/>
       <c r="S14" s="1"/>
-      <c r="T14" s="283" t="s">
+      <c r="T14" s="285" t="s">
         <v>115</v>
       </c>
-      <c r="U14" s="283"/>
-      <c r="V14" s="283"/>
-      <c r="W14" s="283"/>
+      <c r="U14" s="285"/>
+      <c r="V14" s="285"/>
+      <c r="W14" s="285"/>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
@@ -26351,12 +26351,12 @@
       <c r="P15" s="61"/>
       <c r="R15" s="65"/>
       <c r="S15" s="1"/>
-      <c r="T15" s="292" t="s">
+      <c r="T15" s="270" t="s">
         <v>141</v>
       </c>
-      <c r="U15" s="292"/>
-      <c r="V15" s="292"/>
-      <c r="W15" s="292"/>
+      <c r="U15" s="270"/>
+      <c r="V15" s="270"/>
+      <c r="W15" s="270"/>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
@@ -26607,14 +26607,14 @@
     <row r="20" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A20" s="65"/>
       <c r="B20" s="1"/>
-      <c r="C20" s="293" t="s">
+      <c r="C20" s="271" t="s">
         <v>156</v>
       </c>
-      <c r="D20" s="293"/>
-      <c r="E20" s="293"/>
-      <c r="F20" s="293"/>
-      <c r="G20" s="293"/>
-      <c r="H20" s="293"/>
+      <c r="D20" s="271"/>
+      <c r="E20" s="271"/>
+      <c r="F20" s="271"/>
+      <c r="G20" s="271"/>
+      <c r="H20" s="271"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -26659,18 +26659,18 @@
     <row r="21" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A21" s="65"/>
       <c r="B21" s="1"/>
-      <c r="C21" s="294" t="s">
+      <c r="C21" s="272" t="s">
         <v>157</v>
       </c>
-      <c r="D21" s="294"/>
-      <c r="E21" s="294" t="s">
+      <c r="D21" s="272"/>
+      <c r="E21" s="272" t="s">
         <v>158</v>
       </c>
-      <c r="F21" s="294"/>
-      <c r="G21" s="284" t="s">
+      <c r="F21" s="272"/>
+      <c r="G21" s="273" t="s">
         <v>159</v>
       </c>
-      <c r="H21" s="286"/>
+      <c r="H21" s="274"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -27294,11 +27294,11 @@
       <c r="C47" s="33"/>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A48" s="273" t="s">
+      <c r="A48" s="278" t="s">
         <v>137</v>
       </c>
-      <c r="B48" s="273"/>
-      <c r="C48" s="273"/>
+      <c r="B48" s="278"/>
+      <c r="C48" s="278"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B49" s="33"/>
@@ -27308,15 +27308,15 @@
       <c r="A50" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="B50" s="270" t="s">
+      <c r="B50" s="289" t="s">
         <v>84</v>
       </c>
-      <c r="C50" s="271"/>
-      <c r="D50" s="271"/>
-      <c r="E50" s="271"/>
-      <c r="F50" s="271"/>
-      <c r="G50" s="271"/>
-      <c r="H50" s="272"/>
+      <c r="C50" s="290"/>
+      <c r="D50" s="290"/>
+      <c r="E50" s="290"/>
+      <c r="F50" s="290"/>
+      <c r="G50" s="290"/>
+      <c r="H50" s="291"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" s="251" t="s">
@@ -27518,7 +27518,7 @@
       <c r="G63" s="37" t="s">
         <v>102</v>
       </c>
-      <c r="H63" s="291" t="s">
+      <c r="H63" s="277" t="s">
         <v>68</v>
       </c>
     </row>
@@ -27542,7 +27542,7 @@
       <c r="G64" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="H64" s="291"/>
+      <c r="H64" s="277"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" s="51" t="s">
@@ -27689,11 +27689,11 @@
       <c r="H70" s="1"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A71" s="273" t="s">
+      <c r="A71" s="278" t="s">
         <v>138</v>
       </c>
-      <c r="B71" s="273"/>
-      <c r="C71" s="273"/>
+      <c r="B71" s="278"/>
+      <c r="C71" s="278"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B72" s="33"/>
@@ -27816,7 +27816,7 @@
       <c r="C83" s="33"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A84" s="289" t="s">
+      <c r="A84" s="275" t="s">
         <v>117</v>
       </c>
       <c r="B84" s="37" t="s">
@@ -27834,7 +27834,7 @@
       <c r="F84" s="36"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A85" s="290"/>
+      <c r="A85" s="276"/>
       <c r="B85" s="37">
         <v>2020</v>
       </c>
@@ -27928,11 +27928,19 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="T15:W15"/>
-    <mergeCell ref="C20:H20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="B50:H50"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A3:P3"/>
+    <mergeCell ref="R3:AG3"/>
+    <mergeCell ref="AI3:AO3"/>
+    <mergeCell ref="T14:W14"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="T6:W6"/>
+    <mergeCell ref="U7:W7"/>
+    <mergeCell ref="C12:F12"/>
     <mergeCell ref="A84:A85"/>
     <mergeCell ref="A79:C79"/>
     <mergeCell ref="E63:F63"/>
@@ -27940,19 +27948,11 @@
     <mergeCell ref="A64:B64"/>
     <mergeCell ref="A71:C71"/>
     <mergeCell ref="A63:B63"/>
-    <mergeCell ref="R3:AG3"/>
-    <mergeCell ref="AI3:AO3"/>
-    <mergeCell ref="T14:W14"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="T6:W6"/>
-    <mergeCell ref="U7:W7"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="B50:H50"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A3:P3"/>
+    <mergeCell ref="T15:W15"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:H21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
